--- a/artfynd/A 47905-2023 artfynd.xlsx
+++ b/artfynd/A 47905-2023 artfynd.xlsx
@@ -6118,10 +6118,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117711999</v>
+        <v>117711718</v>
       </c>
       <c r="B55" t="n">
-        <v>78125</v>
+        <v>78216</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464823</v>
+        <v>464807</v>
       </c>
       <c r="R55" t="n">
-        <v>6822584</v>
+        <v>6822845</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6220,10 +6220,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117711718</v>
+        <v>117711504</v>
       </c>
       <c r="B56" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6236,21 +6236,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6260,10 +6260,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464807</v>
+        <v>464812</v>
       </c>
       <c r="R56" t="n">
-        <v>6822845</v>
+        <v>6822865</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117711504</v>
+        <v>117711508</v>
       </c>
       <c r="B57" t="n">
         <v>79098</v>
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464812</v>
+        <v>464807</v>
       </c>
       <c r="R57" t="n">
-        <v>6822865</v>
+        <v>6822845</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6424,10 +6424,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117711508</v>
+        <v>117711722</v>
       </c>
       <c r="B58" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6440,21 +6440,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6464,10 +6464,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464807</v>
+        <v>464796</v>
       </c>
       <c r="R58" t="n">
-        <v>6822845</v>
+        <v>6822550</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6526,10 +6526,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117711722</v>
+        <v>117711955</v>
       </c>
       <c r="B59" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6542,21 +6542,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6566,10 +6566,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464796</v>
+        <v>464884</v>
       </c>
       <c r="R59" t="n">
-        <v>6822550</v>
+        <v>6822736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6628,10 +6628,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117711955</v>
+        <v>117711999</v>
       </c>
       <c r="B60" t="n">
-        <v>78480</v>
+        <v>78125</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6644,21 +6644,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464884</v>
+        <v>464823</v>
       </c>
       <c r="R60" t="n">
-        <v>6822736</v>
+        <v>6822584</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7657,10 +7657,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117711664</v>
+        <v>117711622</v>
       </c>
       <c r="B70" t="n">
-        <v>78217</v>
+        <v>79589</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7669,25 +7669,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7697,10 +7697,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464835</v>
+        <v>464806</v>
       </c>
       <c r="R70" t="n">
-        <v>6822696</v>
+        <v>6822865</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7759,10 +7759,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117711622</v>
+        <v>117711664</v>
       </c>
       <c r="B71" t="n">
-        <v>79589</v>
+        <v>78217</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7771,25 +7771,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464806</v>
+        <v>464835</v>
       </c>
       <c r="R71" t="n">
-        <v>6822865</v>
+        <v>6822696</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7963,10 +7963,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117711573</v>
+        <v>117711938</v>
       </c>
       <c r="B73" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7975,41 +7975,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464830</v>
+        <v>464956</v>
       </c>
       <c r="R73" t="n">
-        <v>6822871</v>
+        <v>6822819</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8036,17 +8033,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8055,7 +8047,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8074,10 +8065,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117711514</v>
+        <v>117711573</v>
       </c>
       <c r="B74" t="n">
-        <v>79098</v>
+        <v>79590</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8086,38 +8077,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464789</v>
+        <v>464830</v>
       </c>
       <c r="R74" t="n">
-        <v>6822646</v>
+        <v>6822871</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8152,12 +8146,18 @@
           <t>2024-06-09</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8176,10 +8176,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117711938</v>
+        <v>117711514</v>
       </c>
       <c r="B75" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8192,21 +8192,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8216,10 +8216,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464956</v>
+        <v>464789</v>
       </c>
       <c r="R75" t="n">
-        <v>6822819</v>
+        <v>6822646</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8246,12 +8246,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9094,10 +9094,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117711589</v>
+        <v>117711614</v>
       </c>
       <c r="B84" t="n">
-        <v>79465</v>
+        <v>78506</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9110,21 +9110,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6456</v>
+        <v>6434</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9134,10 +9134,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464773</v>
+        <v>464794</v>
       </c>
       <c r="R84" t="n">
-        <v>6822810</v>
+        <v>6822546</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9196,10 +9196,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117711578</v>
+        <v>117711954</v>
       </c>
       <c r="B85" t="n">
-        <v>57303</v>
+        <v>78480</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9212,42 +9212,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464962</v>
+        <v>464919</v>
       </c>
       <c r="R85" t="n">
-        <v>6822707</v>
+        <v>6822626</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9274,12 +9266,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9306,10 +9298,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117711614</v>
+        <v>117711943</v>
       </c>
       <c r="B86" t="n">
-        <v>78506</v>
+        <v>78480</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9318,25 +9310,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9346,10 +9338,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464794</v>
+        <v>464914</v>
       </c>
       <c r="R86" t="n">
-        <v>6822546</v>
+        <v>6822793</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9376,12 +9368,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9408,10 +9400,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117711954</v>
+        <v>117711561</v>
       </c>
       <c r="B87" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9420,38 +9412,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464919</v>
+        <v>464971</v>
       </c>
       <c r="R87" t="n">
-        <v>6822626</v>
+        <v>6822628</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9478,12 +9473,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9492,6 +9492,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9510,10 +9511,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117711943</v>
+        <v>117711589</v>
       </c>
       <c r="B88" t="n">
-        <v>78480</v>
+        <v>79465</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9522,25 +9523,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9550,10 +9551,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464914</v>
+        <v>464773</v>
       </c>
       <c r="R88" t="n">
-        <v>6822793</v>
+        <v>6822810</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9580,12 +9581,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9612,10 +9613,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117711561</v>
+        <v>117711578</v>
       </c>
       <c r="B89" t="n">
-        <v>79590</v>
+        <v>57303</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9624,30 +9625,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9655,10 +9661,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464971</v>
+        <v>464962</v>
       </c>
       <c r="R89" t="n">
-        <v>6822628</v>
+        <v>6822707</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9693,18 +9699,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47905-2023 artfynd.xlsx
+++ b/artfynd/A 47905-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117711518</v>
+        <v>117711956</v>
       </c>
       <c r="B2" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464788</v>
+        <v>464884</v>
       </c>
       <c r="R2" t="n">
-        <v>6822536</v>
+        <v>6822771</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117711498</v>
+        <v>117711933</v>
       </c>
       <c r="B3" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464862</v>
+        <v>464953</v>
       </c>
       <c r="R3" t="n">
-        <v>6822596</v>
+        <v>6822873</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117711513</v>
+        <v>117711559</v>
       </c>
       <c r="B4" t="n">
-        <v>79098</v>
+        <v>79590</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464787</v>
+        <v>465044</v>
       </c>
       <c r="R4" t="n">
-        <v>6822645</v>
+        <v>6822619</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +952,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,6 +971,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117711499</v>
+        <v>117711664</v>
       </c>
       <c r="B5" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464873</v>
+        <v>464835</v>
       </c>
       <c r="R5" t="n">
-        <v>6822661</v>
+        <v>6822696</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117711671</v>
+        <v>117711578</v>
       </c>
       <c r="B6" t="n">
-        <v>78217</v>
+        <v>57303</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,34 +1108,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464829</v>
+        <v>464962</v>
       </c>
       <c r="R6" t="n">
-        <v>6822493</v>
+        <v>6822707</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1170,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117711751</v>
+        <v>117711412</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1218,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>465064</v>
+        <v>464821</v>
       </c>
       <c r="R7" t="n">
-        <v>6822518</v>
+        <v>6822795</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1272,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,7 +1304,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117711753</v>
+        <v>117711839</v>
       </c>
       <c r="B8" t="n">
         <v>78480</v>
@@ -1327,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464957</v>
+        <v>464908</v>
       </c>
       <c r="R8" t="n">
-        <v>6822668</v>
+        <v>6822788</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1406,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117711502</v>
+        <v>117711512</v>
       </c>
       <c r="B9" t="n">
         <v>79098</v>
@@ -1429,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464832</v>
+        <v>464797</v>
       </c>
       <c r="R9" t="n">
-        <v>6822695</v>
+        <v>6822693</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711556</v>
+        <v>117711667</v>
       </c>
       <c r="B10" t="n">
-        <v>79590</v>
+        <v>78217</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,41 +1520,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464979</v>
+        <v>464785</v>
       </c>
       <c r="R10" t="n">
-        <v>6822661</v>
+        <v>6822821</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,17 +1578,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1583,7 +1592,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1602,10 +1610,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711723</v>
+        <v>117711982</v>
       </c>
       <c r="B11" t="n">
-        <v>78216</v>
+        <v>94503</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,25 +1622,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1642,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464798</v>
+        <v>464829</v>
       </c>
       <c r="R11" t="n">
-        <v>6822515</v>
+        <v>6822608</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,7 +1712,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117711759</v>
+        <v>117711756</v>
       </c>
       <c r="B12" t="n">
         <v>78480</v>
@@ -1744,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>465025</v>
+        <v>464963</v>
       </c>
       <c r="R12" t="n">
-        <v>6822630</v>
+        <v>6822708</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,10 +1814,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117711500</v>
+        <v>117711724</v>
       </c>
       <c r="B13" t="n">
-        <v>79098</v>
+        <v>78216</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1822,21 +1830,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1846,10 +1854,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464862</v>
+        <v>464829</v>
       </c>
       <c r="R13" t="n">
-        <v>6822691</v>
+        <v>6822493</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,7 +1916,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117711495</v>
+        <v>117711510</v>
       </c>
       <c r="B14" t="n">
         <v>79098</v>
@@ -1948,10 +1956,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464963</v>
+        <v>464779</v>
       </c>
       <c r="R14" t="n">
-        <v>6822863</v>
+        <v>6822835</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1978,12 +1986,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2010,10 +2018,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117711663</v>
+        <v>117711617</v>
       </c>
       <c r="B15" t="n">
-        <v>78217</v>
+        <v>79589</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2022,25 +2030,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2050,10 +2058,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464857</v>
+        <v>464933</v>
       </c>
       <c r="R15" t="n">
-        <v>6822584</v>
+        <v>6822795</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2080,12 +2088,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2112,10 +2120,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117711937</v>
+        <v>117711722</v>
       </c>
       <c r="B16" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2128,21 +2136,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2152,10 +2160,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464940</v>
+        <v>464796</v>
       </c>
       <c r="R16" t="n">
-        <v>6822856</v>
+        <v>6822550</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2182,12 +2190,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2214,7 +2222,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117711964</v>
+        <v>117711751</v>
       </c>
       <c r="B17" t="n">
         <v>78480</v>
@@ -2254,10 +2262,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>464854</v>
+        <v>465064</v>
       </c>
       <c r="R17" t="n">
-        <v>6822833</v>
+        <v>6822518</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2284,12 +2292,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2316,7 +2324,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117711965</v>
+        <v>117711972</v>
       </c>
       <c r="B18" t="n">
         <v>78480</v>
@@ -2356,10 +2364,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464847</v>
+        <v>464787</v>
       </c>
       <c r="R18" t="n">
-        <v>6822842</v>
+        <v>6822809</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2426,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117711961</v>
+        <v>117711496</v>
       </c>
       <c r="B19" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2442,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2466,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464869</v>
+        <v>464827</v>
       </c>
       <c r="R19" t="n">
-        <v>6822820</v>
+        <v>6822493</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,10 +2528,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711939</v>
+        <v>117711378</v>
       </c>
       <c r="B20" t="n">
-        <v>78480</v>
+        <v>5186</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2532,38 +2540,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464944</v>
+        <v>465023</v>
       </c>
       <c r="R20" t="n">
-        <v>6822809</v>
+        <v>6822630</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2604,6 +2621,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2622,10 +2640,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117711959</v>
+        <v>117711526</v>
       </c>
       <c r="B21" t="n">
-        <v>78480</v>
+        <v>79069</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,21 +2656,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2680,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464897</v>
+        <v>464802</v>
       </c>
       <c r="R21" t="n">
-        <v>6822794</v>
+        <v>6822558</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2742,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117711466</v>
+        <v>117711753</v>
       </c>
       <c r="B22" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,21 +2758,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2782,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464808</v>
+        <v>464957</v>
       </c>
       <c r="R22" t="n">
-        <v>6822742</v>
+        <v>6822668</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2844,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117711509</v>
+        <v>117711998</v>
       </c>
       <c r="B23" t="n">
-        <v>79098</v>
+        <v>78125</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2860,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2884,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464812</v>
+        <v>464781</v>
       </c>
       <c r="R23" t="n">
-        <v>6822825</v>
+        <v>6822679</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,10 +2946,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117711558</v>
+        <v>117711932</v>
       </c>
       <c r="B24" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2940,41 +2958,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465071</v>
+        <v>464956</v>
       </c>
       <c r="R24" t="n">
-        <v>6822559</v>
+        <v>6822869</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3009,18 +3024,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3039,10 +3048,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117711982</v>
+        <v>117711721</v>
       </c>
       <c r="B25" t="n">
-        <v>94503</v>
+        <v>78216</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3051,25 +3060,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3079,10 +3088,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464829</v>
+        <v>464811</v>
       </c>
       <c r="R25" t="n">
-        <v>6822608</v>
+        <v>6822558</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,10 +3150,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117711997</v>
+        <v>117711519</v>
       </c>
       <c r="B26" t="n">
-        <v>78125</v>
+        <v>79098</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3157,21 +3166,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3181,10 +3190,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464790</v>
+        <v>464829</v>
       </c>
       <c r="R26" t="n">
-        <v>6822679</v>
+        <v>6822493</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3243,7 +3252,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117711497</v>
+        <v>117711502</v>
       </c>
       <c r="B27" t="n">
         <v>79098</v>
@@ -3283,10 +3292,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464842</v>
+        <v>464832</v>
       </c>
       <c r="R27" t="n">
-        <v>6822509</v>
+        <v>6822695</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3345,10 +3354,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117711750</v>
+        <v>117711561</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3357,38 +3366,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>465035</v>
+        <v>464971</v>
       </c>
       <c r="R28" t="n">
-        <v>6822499</v>
+        <v>6822628</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3423,12 +3435,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3447,10 +3465,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117711953</v>
+        <v>117711718</v>
       </c>
       <c r="B29" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3463,21 +3481,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3487,10 +3505,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464900</v>
+        <v>464807</v>
       </c>
       <c r="R29" t="n">
-        <v>6822625</v>
+        <v>6822845</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3549,7 +3567,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117711519</v>
+        <v>117711498</v>
       </c>
       <c r="B30" t="n">
         <v>79098</v>
@@ -3589,10 +3607,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464829</v>
+        <v>464862</v>
       </c>
       <c r="R30" t="n">
-        <v>6822493</v>
+        <v>6822596</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3651,10 +3669,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117711972</v>
+        <v>117711558</v>
       </c>
       <c r="B31" t="n">
-        <v>78480</v>
+        <v>79590</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3663,38 +3681,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464787</v>
+        <v>465071</v>
       </c>
       <c r="R31" t="n">
-        <v>6822809</v>
+        <v>6822559</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3721,12 +3742,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3735,6 +3761,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3753,10 +3780,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117711670</v>
+        <v>117711957</v>
       </c>
       <c r="B32" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3769,21 +3796,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3793,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464796</v>
+        <v>464891</v>
       </c>
       <c r="R32" t="n">
-        <v>6822550</v>
+        <v>6822781</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3855,10 +3882,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117711621</v>
+        <v>117711759</v>
       </c>
       <c r="B33" t="n">
-        <v>79589</v>
+        <v>78480</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3867,25 +3894,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3895,10 +3922,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464960</v>
+        <v>465025</v>
       </c>
       <c r="R33" t="n">
-        <v>6822857</v>
+        <v>6822630</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3957,10 +3984,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117711378</v>
+        <v>117711413</v>
       </c>
       <c r="B34" t="n">
-        <v>5186</v>
+        <v>78514</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3969,47 +3996,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>465023</v>
+        <v>464796</v>
       </c>
       <c r="R34" t="n">
-        <v>6822630</v>
+        <v>6822812</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,12 +4054,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4050,7 +4068,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4069,10 +4086,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117711724</v>
+        <v>117711959</v>
       </c>
       <c r="B35" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4085,21 +4102,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4109,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464829</v>
+        <v>464897</v>
       </c>
       <c r="R35" t="n">
-        <v>6822493</v>
+        <v>6822794</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4171,10 +4188,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117711749</v>
+        <v>117711466</v>
       </c>
       <c r="B36" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4187,21 +4204,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4211,10 +4228,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>465020</v>
+        <v>464808</v>
       </c>
       <c r="R36" t="n">
-        <v>6822478</v>
+        <v>6822742</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4273,10 +4290,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117711719</v>
+        <v>117711504</v>
       </c>
       <c r="B37" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4289,21 +4306,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4313,10 +4330,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464779</v>
+        <v>464812</v>
       </c>
       <c r="R37" t="n">
-        <v>6822837</v>
+        <v>6822865</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4375,10 +4392,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117711411</v>
+        <v>117711695</v>
       </c>
       <c r="B38" t="n">
-        <v>78514</v>
+        <v>78216</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4391,21 +4408,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4415,10 +4432,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464887</v>
+        <v>464953</v>
       </c>
       <c r="R38" t="n">
-        <v>6822782</v>
+        <v>6822673</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4445,12 +4462,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4477,7 +4494,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117711962</v>
+        <v>117711964</v>
       </c>
       <c r="B39" t="n">
         <v>78480</v>
@@ -4517,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464870</v>
+        <v>464854</v>
       </c>
       <c r="R39" t="n">
-        <v>6822808</v>
+        <v>6822833</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4579,10 +4596,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117711932</v>
+        <v>117711723</v>
       </c>
       <c r="B40" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4595,21 +4612,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4619,10 +4636,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464956</v>
+        <v>464798</v>
       </c>
       <c r="R40" t="n">
-        <v>6822869</v>
+        <v>6822515</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4649,12 +4666,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4681,10 +4698,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117711942</v>
+        <v>117711614</v>
       </c>
       <c r="B41" t="n">
-        <v>78480</v>
+        <v>78506</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4693,25 +4710,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4721,10 +4738,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464917</v>
+        <v>464794</v>
       </c>
       <c r="R41" t="n">
-        <v>6822797</v>
+        <v>6822546</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4751,12 +4768,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4783,7 +4800,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117711510</v>
+        <v>117711495</v>
       </c>
       <c r="B42" t="n">
         <v>79098</v>
@@ -4823,10 +4840,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464779</v>
+        <v>464963</v>
       </c>
       <c r="R42" t="n">
-        <v>6822835</v>
+        <v>6822863</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4853,12 +4870,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4885,10 +4902,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117711515</v>
+        <v>117711944</v>
       </c>
       <c r="B43" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4901,21 +4918,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4925,10 +4942,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464791</v>
+        <v>464915</v>
       </c>
       <c r="R43" t="n">
-        <v>6822636</v>
+        <v>6822788</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4955,12 +4972,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4987,10 +5004,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117711613</v>
+        <v>117711621</v>
       </c>
       <c r="B44" t="n">
-        <v>78506</v>
+        <v>79589</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5003,21 +5020,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6434</v>
+        <v>6461</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5027,10 +5044,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464776</v>
+        <v>464960</v>
       </c>
       <c r="R44" t="n">
-        <v>6822609</v>
+        <v>6822857</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5057,12 +5074,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5089,7 +5106,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117711512</v>
+        <v>117711517</v>
       </c>
       <c r="B45" t="n">
         <v>79098</v>
@@ -5129,10 +5146,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464797</v>
+        <v>464796</v>
       </c>
       <c r="R45" t="n">
-        <v>6822693</v>
+        <v>6822550</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5191,10 +5208,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117711415</v>
+        <v>117711573</v>
       </c>
       <c r="B46" t="n">
-        <v>78514</v>
+        <v>79590</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5203,38 +5220,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464750</v>
+        <v>464830</v>
       </c>
       <c r="R46" t="n">
-        <v>6822791</v>
+        <v>6822871</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5269,12 +5289,18 @@
           <t>2024-06-09</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5293,10 +5319,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117711998</v>
+        <v>117711943</v>
       </c>
       <c r="B47" t="n">
-        <v>78125</v>
+        <v>78480</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5309,21 +5335,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5333,10 +5359,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464781</v>
+        <v>464914</v>
       </c>
       <c r="R47" t="n">
-        <v>6822679</v>
+        <v>6822793</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5363,12 +5389,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5395,7 +5421,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117711933</v>
+        <v>117711960</v>
       </c>
       <c r="B48" t="n">
         <v>78480</v>
@@ -5435,10 +5461,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464953</v>
+        <v>464895</v>
       </c>
       <c r="R48" t="n">
-        <v>6822873</v>
+        <v>6822799</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5465,12 +5491,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5497,10 +5523,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117711517</v>
+        <v>117711939</v>
       </c>
       <c r="B49" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5513,21 +5539,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5537,10 +5563,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464796</v>
+        <v>464944</v>
       </c>
       <c r="R49" t="n">
-        <v>6822550</v>
+        <v>6822809</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5567,12 +5593,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5599,7 +5625,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117711839</v>
+        <v>117711938</v>
       </c>
       <c r="B50" t="n">
         <v>78480</v>
@@ -5639,10 +5665,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464908</v>
+        <v>464956</v>
       </c>
       <c r="R50" t="n">
-        <v>6822788</v>
+        <v>6822819</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5701,10 +5727,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117711756</v>
+        <v>117711411</v>
       </c>
       <c r="B51" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5717,21 +5743,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5741,10 +5767,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464963</v>
+        <v>464887</v>
       </c>
       <c r="R51" t="n">
-        <v>6822708</v>
+        <v>6822782</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5771,12 +5797,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5803,10 +5829,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117711757</v>
+        <v>117711999</v>
       </c>
       <c r="B52" t="n">
-        <v>78480</v>
+        <v>78125</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5819,21 +5845,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5843,10 +5869,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464957</v>
+        <v>464823</v>
       </c>
       <c r="R52" t="n">
-        <v>6822685</v>
+        <v>6822584</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5873,12 +5899,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5905,7 +5931,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117711944</v>
+        <v>117711942</v>
       </c>
       <c r="B53" t="n">
         <v>78480</v>
@@ -5945,10 +5971,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464915</v>
+        <v>464917</v>
       </c>
       <c r="R53" t="n">
-        <v>6822788</v>
+        <v>6822797</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6007,10 +6033,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117711570</v>
+        <v>117711755</v>
       </c>
       <c r="B54" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6019,41 +6045,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464946</v>
+        <v>464952</v>
       </c>
       <c r="R54" t="n">
-        <v>6822832</v>
+        <v>6822727</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6088,18 +6111,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6118,10 +6135,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117711718</v>
+        <v>117711500</v>
       </c>
       <c r="B55" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6134,21 +6151,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6158,10 +6175,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464807</v>
+        <v>464862</v>
       </c>
       <c r="R55" t="n">
-        <v>6822845</v>
+        <v>6822691</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6220,10 +6237,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117711504</v>
+        <v>117711670</v>
       </c>
       <c r="B56" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6236,21 +6253,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6260,10 +6277,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464812</v>
+        <v>464796</v>
       </c>
       <c r="R56" t="n">
-        <v>6822865</v>
+        <v>6822550</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6322,10 +6339,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117711508</v>
+        <v>117711968</v>
       </c>
       <c r="B57" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6338,21 +6355,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6362,10 +6379,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464807</v>
+        <v>464845</v>
       </c>
       <c r="R57" t="n">
-        <v>6822845</v>
+        <v>6822867</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6424,10 +6441,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117711722</v>
+        <v>117711556</v>
       </c>
       <c r="B58" t="n">
-        <v>78216</v>
+        <v>79590</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6436,38 +6453,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464796</v>
+        <v>464979</v>
       </c>
       <c r="R58" t="n">
-        <v>6822550</v>
+        <v>6822661</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6494,12 +6514,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6508,6 +6533,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6526,10 +6552,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117711955</v>
+        <v>117711719</v>
       </c>
       <c r="B59" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6542,21 +6568,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6566,10 +6592,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464884</v>
+        <v>464779</v>
       </c>
       <c r="R59" t="n">
-        <v>6822736</v>
+        <v>6822837</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6628,10 +6654,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117711999</v>
+        <v>117711613</v>
       </c>
       <c r="B60" t="n">
-        <v>78125</v>
+        <v>78506</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6640,25 +6666,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6668,10 +6694,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464823</v>
+        <v>464776</v>
       </c>
       <c r="R60" t="n">
-        <v>6822584</v>
+        <v>6822609</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6730,10 +6756,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117711559</v>
+        <v>117711509</v>
       </c>
       <c r="B61" t="n">
-        <v>79590</v>
+        <v>79098</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6742,41 +6768,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>465044</v>
+        <v>464812</v>
       </c>
       <c r="R61" t="n">
-        <v>6822619</v>
+        <v>6822825</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6803,17 +6826,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6822,7 +6840,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6841,10 +6858,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117711968</v>
+        <v>117711415</v>
       </c>
       <c r="B62" t="n">
-        <v>78480</v>
+        <v>78514</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6857,21 +6874,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6881,10 +6898,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464845</v>
+        <v>464750</v>
       </c>
       <c r="R62" t="n">
-        <v>6822867</v>
+        <v>6822791</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6943,10 +6960,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117711695</v>
+        <v>117711937</v>
       </c>
       <c r="B63" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6959,21 +6976,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6983,10 +7000,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464953</v>
+        <v>464940</v>
       </c>
       <c r="R63" t="n">
-        <v>6822673</v>
+        <v>6822856</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7045,10 +7062,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117711496</v>
+        <v>117711749</v>
       </c>
       <c r="B64" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7061,21 +7078,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7085,10 +7102,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464827</v>
+        <v>465020</v>
       </c>
       <c r="R64" t="n">
-        <v>6822493</v>
+        <v>6822478</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7115,12 +7132,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7147,10 +7164,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117711516</v>
+        <v>117711750</v>
       </c>
       <c r="B65" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7163,21 +7180,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7187,10 +7204,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464802</v>
+        <v>465035</v>
       </c>
       <c r="R65" t="n">
-        <v>6822558</v>
+        <v>6822499</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7217,12 +7234,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7249,10 +7266,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117711667</v>
+        <v>117711570</v>
       </c>
       <c r="B66" t="n">
-        <v>78217</v>
+        <v>79590</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7261,38 +7278,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464785</v>
+        <v>464946</v>
       </c>
       <c r="R66" t="n">
-        <v>6822821</v>
+        <v>6822832</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7319,12 +7339,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7333,6 +7358,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7351,10 +7377,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117711957</v>
+        <v>117711513</v>
       </c>
       <c r="B67" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7367,21 +7393,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7391,10 +7417,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464891</v>
+        <v>464787</v>
       </c>
       <c r="R67" t="n">
-        <v>6822781</v>
+        <v>6822645</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7453,10 +7479,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117711840</v>
+        <v>117711694</v>
       </c>
       <c r="B68" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7469,21 +7495,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7493,10 +7519,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464918</v>
+        <v>465016</v>
       </c>
       <c r="R68" t="n">
-        <v>6822794</v>
+        <v>6822483</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7555,10 +7581,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117711617</v>
+        <v>117711515</v>
       </c>
       <c r="B69" t="n">
-        <v>79589</v>
+        <v>79098</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7567,25 +7593,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7595,10 +7621,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464933</v>
+        <v>464791</v>
       </c>
       <c r="R69" t="n">
-        <v>6822795</v>
+        <v>6822636</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7625,12 +7651,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7759,10 +7785,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117711664</v>
+        <v>117711953</v>
       </c>
       <c r="B71" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7775,21 +7801,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7799,10 +7825,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464835</v>
+        <v>464900</v>
       </c>
       <c r="R71" t="n">
-        <v>6822696</v>
+        <v>6822625</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7861,10 +7887,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117712000</v>
+        <v>117711954</v>
       </c>
       <c r="B72" t="n">
-        <v>78125</v>
+        <v>78480</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7877,21 +7903,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7901,10 +7927,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464806</v>
+        <v>464919</v>
       </c>
       <c r="R72" t="n">
-        <v>6822556</v>
+        <v>6822626</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7963,10 +7989,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117711938</v>
+        <v>117711663</v>
       </c>
       <c r="B73" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7979,21 +8005,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8003,10 +8029,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464956</v>
+        <v>464857</v>
       </c>
       <c r="R73" t="n">
-        <v>6822819</v>
+        <v>6822584</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8033,12 +8059,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8065,10 +8091,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117711573</v>
+        <v>117711965</v>
       </c>
       <c r="B74" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8077,41 +8103,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464830</v>
+        <v>464847</v>
       </c>
       <c r="R74" t="n">
-        <v>6822871</v>
+        <v>6822842</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8146,18 +8169,12 @@
           <t>2024-06-09</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8176,10 +8193,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117711514</v>
+        <v>117711955</v>
       </c>
       <c r="B75" t="n">
-        <v>79098</v>
+        <v>78480</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8192,21 +8209,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8216,10 +8233,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464789</v>
+        <v>464884</v>
       </c>
       <c r="R75" t="n">
-        <v>6822646</v>
+        <v>6822736</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8278,10 +8295,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117711755</v>
+        <v>117711671</v>
       </c>
       <c r="B76" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8294,21 +8311,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8318,10 +8335,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464952</v>
+        <v>464829</v>
       </c>
       <c r="R76" t="n">
-        <v>6822727</v>
+        <v>6822493</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8348,12 +8365,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8380,10 +8397,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117711960</v>
+        <v>117711508</v>
       </c>
       <c r="B77" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8396,21 +8413,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8420,10 +8437,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464895</v>
+        <v>464807</v>
       </c>
       <c r="R77" t="n">
-        <v>6822799</v>
+        <v>6822845</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8482,10 +8499,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117711526</v>
+        <v>117711499</v>
       </c>
       <c r="B78" t="n">
-        <v>79069</v>
+        <v>79098</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8498,21 +8515,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8522,10 +8539,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464802</v>
+        <v>464873</v>
       </c>
       <c r="R78" t="n">
-        <v>6822558</v>
+        <v>6822661</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8584,10 +8601,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117711413</v>
+        <v>117711497</v>
       </c>
       <c r="B79" t="n">
-        <v>78514</v>
+        <v>79098</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8600,21 +8617,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8624,10 +8641,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464796</v>
+        <v>464842</v>
       </c>
       <c r="R79" t="n">
-        <v>6822812</v>
+        <v>6822509</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8686,10 +8703,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117711412</v>
+        <v>117711997</v>
       </c>
       <c r="B80" t="n">
-        <v>78514</v>
+        <v>78125</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8702,21 +8719,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>353</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8726,10 +8743,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464821</v>
+        <v>464790</v>
       </c>
       <c r="R80" t="n">
-        <v>6822795</v>
+        <v>6822679</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8788,10 +8805,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117711694</v>
+        <v>117711757</v>
       </c>
       <c r="B81" t="n">
-        <v>78216</v>
+        <v>78480</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8804,21 +8821,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8828,10 +8845,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>465016</v>
+        <v>464957</v>
       </c>
       <c r="R81" t="n">
-        <v>6822483</v>
+        <v>6822685</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8890,10 +8907,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117711956</v>
+        <v>117711514</v>
       </c>
       <c r="B82" t="n">
-        <v>78480</v>
+        <v>79098</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8906,21 +8923,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8930,10 +8947,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464884</v>
+        <v>464789</v>
       </c>
       <c r="R82" t="n">
-        <v>6822771</v>
+        <v>6822646</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8992,10 +9009,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117711668</v>
+        <v>117711516</v>
       </c>
       <c r="B83" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9008,21 +9025,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9032,10 +9049,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464814</v>
+        <v>464802</v>
       </c>
       <c r="R83" t="n">
-        <v>6822561</v>
+        <v>6822558</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9094,10 +9111,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117711614</v>
+        <v>117712000</v>
       </c>
       <c r="B84" t="n">
-        <v>78506</v>
+        <v>78125</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9106,25 +9123,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9134,10 +9151,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464794</v>
+        <v>464806</v>
       </c>
       <c r="R84" t="n">
-        <v>6822546</v>
+        <v>6822556</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9196,7 +9213,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117711954</v>
+        <v>117711962</v>
       </c>
       <c r="B85" t="n">
         <v>78480</v>
@@ -9236,10 +9253,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464919</v>
+        <v>464870</v>
       </c>
       <c r="R85" t="n">
-        <v>6822626</v>
+        <v>6822808</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9298,7 +9315,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117711943</v>
+        <v>117711840</v>
       </c>
       <c r="B86" t="n">
         <v>78480</v>
@@ -9338,10 +9355,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464914</v>
+        <v>464918</v>
       </c>
       <c r="R86" t="n">
-        <v>6822793</v>
+        <v>6822794</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9400,10 +9417,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117711561</v>
+        <v>117711961</v>
       </c>
       <c r="B87" t="n">
-        <v>79590</v>
+        <v>78480</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9412,41 +9429,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464971</v>
+        <v>464869</v>
       </c>
       <c r="R87" t="n">
-        <v>6822628</v>
+        <v>6822820</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9473,17 +9487,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9492,7 +9501,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9511,10 +9519,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117711589</v>
+        <v>117711518</v>
       </c>
       <c r="B88" t="n">
-        <v>79465</v>
+        <v>79098</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9523,25 +9531,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9551,10 +9559,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464773</v>
+        <v>464788</v>
       </c>
       <c r="R88" t="n">
-        <v>6822810</v>
+        <v>6822536</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9613,10 +9621,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117711578</v>
+        <v>117711589</v>
       </c>
       <c r="B89" t="n">
-        <v>57303</v>
+        <v>79465</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9625,46 +9633,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464962</v>
+        <v>464773</v>
       </c>
       <c r="R89" t="n">
-        <v>6822707</v>
+        <v>6822810</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9691,12 +9691,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9723,10 +9723,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117711721</v>
+        <v>117711668</v>
       </c>
       <c r="B90" t="n">
-        <v>78216</v>
+        <v>78217</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9739,21 +9739,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464811</v>
+        <v>464814</v>
       </c>
       <c r="R90" t="n">
-        <v>6822558</v>
+        <v>6822561</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 47905-2023 artfynd.xlsx
+++ b/artfynd/A 47905-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117711956</v>
+        <v>117711939</v>
       </c>
       <c r="B2" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464884</v>
+        <v>464944</v>
       </c>
       <c r="R2" t="n">
-        <v>6822771</v>
+        <v>6822809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117711933</v>
+        <v>117711965</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464953</v>
+        <v>464847</v>
       </c>
       <c r="R3" t="n">
-        <v>6822873</v>
+        <v>6822842</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117711559</v>
+        <v>117711497</v>
       </c>
       <c r="B4" t="n">
-        <v>79590</v>
+        <v>79100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>465044</v>
+        <v>464842</v>
       </c>
       <c r="R4" t="n">
-        <v>6822619</v>
+        <v>6822509</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -952,17 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117711664</v>
+        <v>117711671</v>
       </c>
       <c r="B5" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464835</v>
+        <v>464829</v>
       </c>
       <c r="R5" t="n">
-        <v>6822696</v>
+        <v>6822493</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117711578</v>
+        <v>117711933</v>
       </c>
       <c r="B6" t="n">
-        <v>57303</v>
+        <v>78482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,42 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464962</v>
+        <v>464953</v>
       </c>
       <c r="R6" t="n">
-        <v>6822707</v>
+        <v>6822873</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1202,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117711412</v>
+        <v>117711953</v>
       </c>
       <c r="B7" t="n">
-        <v>78514</v>
+        <v>78482</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1242,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464821</v>
+        <v>464900</v>
       </c>
       <c r="R7" t="n">
-        <v>6822795</v>
+        <v>6822625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117711839</v>
+        <v>117711561</v>
       </c>
       <c r="B8" t="n">
-        <v>78480</v>
+        <v>79592</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1316,38 +1299,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464908</v>
+        <v>464971</v>
       </c>
       <c r="R8" t="n">
-        <v>6822788</v>
+        <v>6822628</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,12 +1368,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1406,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117711512</v>
+        <v>117711617</v>
       </c>
       <c r="B9" t="n">
-        <v>79098</v>
+        <v>79591</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1418,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464797</v>
+        <v>464933</v>
       </c>
       <c r="R9" t="n">
-        <v>6822693</v>
+        <v>6822795</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,12 +1468,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711667</v>
+        <v>117711415</v>
       </c>
       <c r="B10" t="n">
-        <v>78217</v>
+        <v>78516</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1524,21 +1516,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1548,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464785</v>
+        <v>464750</v>
       </c>
       <c r="R10" t="n">
-        <v>6822821</v>
+        <v>6822791</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711982</v>
+        <v>117711495</v>
       </c>
       <c r="B11" t="n">
-        <v>94503</v>
+        <v>79100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1622,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1650,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464829</v>
+        <v>464963</v>
       </c>
       <c r="R11" t="n">
-        <v>6822608</v>
+        <v>6822863</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,12 +1672,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1712,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117711756</v>
+        <v>117711721</v>
       </c>
       <c r="B12" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1728,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464963</v>
+        <v>464811</v>
       </c>
       <c r="R12" t="n">
-        <v>6822708</v>
+        <v>6822558</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,12 +1774,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1814,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117711724</v>
+        <v>117711517</v>
       </c>
       <c r="B13" t="n">
-        <v>78216</v>
+        <v>79100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1830,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1854,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464829</v>
+        <v>464796</v>
       </c>
       <c r="R13" t="n">
-        <v>6822493</v>
+        <v>6822550</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117711510</v>
+        <v>117711694</v>
       </c>
       <c r="B14" t="n">
-        <v>79098</v>
+        <v>78218</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1932,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1956,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464779</v>
+        <v>465016</v>
       </c>
       <c r="R14" t="n">
-        <v>6822835</v>
+        <v>6822483</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1986,12 +1978,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2018,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117711617</v>
+        <v>117711502</v>
       </c>
       <c r="B15" t="n">
-        <v>79589</v>
+        <v>79100</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2030,25 +2022,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2058,10 +2050,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464933</v>
+        <v>464832</v>
       </c>
       <c r="R15" t="n">
-        <v>6822795</v>
+        <v>6822695</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,12 +2080,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2120,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117711722</v>
+        <v>117711972</v>
       </c>
       <c r="B16" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2136,21 +2128,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2160,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464796</v>
+        <v>464787</v>
       </c>
       <c r="R16" t="n">
-        <v>6822550</v>
+        <v>6822809</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2222,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117711751</v>
+        <v>117711959</v>
       </c>
       <c r="B17" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,10 +2254,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465064</v>
+        <v>464897</v>
       </c>
       <c r="R17" t="n">
-        <v>6822518</v>
+        <v>6822794</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,12 +2284,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2324,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117711972</v>
+        <v>117711504</v>
       </c>
       <c r="B18" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2340,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2364,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464787</v>
+        <v>464812</v>
       </c>
       <c r="R18" t="n">
-        <v>6822809</v>
+        <v>6822865</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2426,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117711496</v>
+        <v>117711750</v>
       </c>
       <c r="B19" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2442,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2466,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>464827</v>
+        <v>465035</v>
       </c>
       <c r="R19" t="n">
-        <v>6822493</v>
+        <v>6822499</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2496,12 +2488,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2528,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711378</v>
+        <v>117711512</v>
       </c>
       <c r="B20" t="n">
-        <v>5186</v>
+        <v>79100</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2540,47 +2532,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>465023</v>
+        <v>464797</v>
       </c>
       <c r="R20" t="n">
-        <v>6822630</v>
+        <v>6822693</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2607,12 +2590,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2621,7 +2604,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2640,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117711526</v>
+        <v>117711719</v>
       </c>
       <c r="B21" t="n">
-        <v>79069</v>
+        <v>78218</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2656,21 +2638,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2680,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464802</v>
+        <v>464779</v>
       </c>
       <c r="R21" t="n">
-        <v>6822558</v>
+        <v>6822837</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2742,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117711753</v>
+        <v>117711961</v>
       </c>
       <c r="B22" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2782,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464957</v>
+        <v>464869</v>
       </c>
       <c r="R22" t="n">
-        <v>6822668</v>
+        <v>6822820</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2812,12 +2794,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2844,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117711998</v>
+        <v>117711670</v>
       </c>
       <c r="B23" t="n">
-        <v>78125</v>
+        <v>78219</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2860,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2884,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464781</v>
+        <v>464796</v>
       </c>
       <c r="R23" t="n">
-        <v>6822679</v>
+        <v>6822550</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2946,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117711932</v>
+        <v>117711510</v>
       </c>
       <c r="B24" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2962,21 +2944,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2986,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>464956</v>
+        <v>464779</v>
       </c>
       <c r="R24" t="n">
-        <v>6822869</v>
+        <v>6822835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3016,12 +2998,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3048,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117711721</v>
+        <v>117712000</v>
       </c>
       <c r="B25" t="n">
-        <v>78216</v>
+        <v>78127</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3064,21 +3046,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3088,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464811</v>
+        <v>464806</v>
       </c>
       <c r="R25" t="n">
-        <v>6822558</v>
+        <v>6822556</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117711519</v>
+        <v>117711749</v>
       </c>
       <c r="B26" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3166,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3190,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464829</v>
+        <v>465020</v>
       </c>
       <c r="R26" t="n">
-        <v>6822493</v>
+        <v>6822478</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3220,12 +3202,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3252,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117711502</v>
+        <v>117711723</v>
       </c>
       <c r="B27" t="n">
-        <v>79098</v>
+        <v>78218</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3268,21 +3250,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3292,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464832</v>
+        <v>464798</v>
       </c>
       <c r="R27" t="n">
-        <v>6822695</v>
+        <v>6822515</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3354,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117711561</v>
+        <v>117711960</v>
       </c>
       <c r="B28" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3366,41 +3348,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464971</v>
+        <v>464895</v>
       </c>
       <c r="R28" t="n">
-        <v>6822628</v>
+        <v>6822799</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3427,17 +3406,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3446,7 +3420,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3465,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117711718</v>
+        <v>117711932</v>
       </c>
       <c r="B29" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3481,21 +3454,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3505,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464807</v>
+        <v>464956</v>
       </c>
       <c r="R29" t="n">
-        <v>6822845</v>
+        <v>6822869</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3535,12 +3508,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3567,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117711498</v>
+        <v>117711695</v>
       </c>
       <c r="B30" t="n">
-        <v>79098</v>
+        <v>78218</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3583,21 +3556,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3607,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464862</v>
+        <v>464953</v>
       </c>
       <c r="R30" t="n">
-        <v>6822596</v>
+        <v>6822673</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3637,12 +3610,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3669,10 +3642,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117711558</v>
+        <v>117711759</v>
       </c>
       <c r="B31" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3681,41 +3654,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>465071</v>
+        <v>465025</v>
       </c>
       <c r="R31" t="n">
-        <v>6822559</v>
+        <v>6822630</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3750,18 +3720,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3780,10 +3744,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117711957</v>
+        <v>117711466</v>
       </c>
       <c r="B32" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3796,21 +3760,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3820,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464891</v>
+        <v>464808</v>
       </c>
       <c r="R32" t="n">
-        <v>6822781</v>
+        <v>6822742</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3850,12 +3814,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3882,10 +3846,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117711759</v>
+        <v>117711944</v>
       </c>
       <c r="B33" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3922,10 +3886,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>465025</v>
+        <v>464915</v>
       </c>
       <c r="R33" t="n">
-        <v>6822630</v>
+        <v>6822788</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3984,10 +3948,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117711413</v>
+        <v>117711559</v>
       </c>
       <c r="B34" t="n">
-        <v>78514</v>
+        <v>79592</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3996,38 +3960,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464796</v>
+        <v>465044</v>
       </c>
       <c r="R34" t="n">
-        <v>6822812</v>
+        <v>6822619</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4054,12 +4021,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4068,6 +4040,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4086,10 +4059,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117711959</v>
+        <v>117711937</v>
       </c>
       <c r="B35" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4126,10 +4099,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464897</v>
+        <v>464940</v>
       </c>
       <c r="R35" t="n">
-        <v>6822794</v>
+        <v>6822856</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4156,12 +4129,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4188,10 +4161,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117711466</v>
+        <v>117711499</v>
       </c>
       <c r="B36" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4228,10 +4201,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464808</v>
+        <v>464873</v>
       </c>
       <c r="R36" t="n">
-        <v>6822742</v>
+        <v>6822661</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4258,12 +4231,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4290,10 +4263,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117711504</v>
+        <v>117711570</v>
       </c>
       <c r="B37" t="n">
-        <v>79098</v>
+        <v>79592</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4302,38 +4275,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464812</v>
+        <v>464946</v>
       </c>
       <c r="R37" t="n">
-        <v>6822865</v>
+        <v>6822832</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4360,12 +4336,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4374,6 +4355,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4392,10 +4374,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117711695</v>
+        <v>117711942</v>
       </c>
       <c r="B38" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4408,21 +4390,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4432,10 +4414,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464953</v>
+        <v>464917</v>
       </c>
       <c r="R38" t="n">
-        <v>6822673</v>
+        <v>6822797</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4494,10 +4476,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117711964</v>
+        <v>117711718</v>
       </c>
       <c r="B39" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4510,21 +4492,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4534,10 +4516,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464854</v>
+        <v>464807</v>
       </c>
       <c r="R39" t="n">
-        <v>6822833</v>
+        <v>6822845</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4596,10 +4578,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117711723</v>
+        <v>117711413</v>
       </c>
       <c r="B40" t="n">
-        <v>78216</v>
+        <v>78516</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4612,21 +4594,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4636,10 +4618,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464798</v>
+        <v>464796</v>
       </c>
       <c r="R40" t="n">
-        <v>6822515</v>
+        <v>6822812</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4698,10 +4680,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117711614</v>
+        <v>117711411</v>
       </c>
       <c r="B41" t="n">
-        <v>78506</v>
+        <v>78516</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4710,25 +4692,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6434</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4738,10 +4720,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464794</v>
+        <v>464887</v>
       </c>
       <c r="R41" t="n">
-        <v>6822546</v>
+        <v>6822782</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4800,10 +4782,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117711495</v>
+        <v>117711839</v>
       </c>
       <c r="B42" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4816,21 +4798,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4840,10 +4822,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464963</v>
+        <v>464908</v>
       </c>
       <c r="R42" t="n">
-        <v>6822863</v>
+        <v>6822788</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4902,10 +4884,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117711944</v>
+        <v>117711621</v>
       </c>
       <c r="B43" t="n">
-        <v>78480</v>
+        <v>79591</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4914,25 +4896,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4942,10 +4924,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464915</v>
+        <v>464960</v>
       </c>
       <c r="R43" t="n">
-        <v>6822788</v>
+        <v>6822857</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5004,10 +4986,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117711621</v>
+        <v>117711954</v>
       </c>
       <c r="B44" t="n">
-        <v>79589</v>
+        <v>78482</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5016,25 +4998,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5044,10 +5026,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464960</v>
+        <v>464919</v>
       </c>
       <c r="R44" t="n">
-        <v>6822857</v>
+        <v>6822626</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5074,12 +5056,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5106,10 +5088,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117711517</v>
+        <v>117711518</v>
       </c>
       <c r="B45" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5146,10 +5128,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464796</v>
+        <v>464788</v>
       </c>
       <c r="R45" t="n">
-        <v>6822550</v>
+        <v>6822536</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5208,10 +5190,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117711573</v>
+        <v>117711509</v>
       </c>
       <c r="B46" t="n">
-        <v>79590</v>
+        <v>79100</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5220,41 +5202,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464830</v>
+        <v>464812</v>
       </c>
       <c r="R46" t="n">
-        <v>6822871</v>
+        <v>6822825</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5289,18 +5268,12 @@
           <t>2024-06-09</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5319,10 +5292,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117711943</v>
+        <v>117711668</v>
       </c>
       <c r="B47" t="n">
-        <v>78480</v>
+        <v>78219</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5335,21 +5308,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5359,10 +5332,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464914</v>
+        <v>464814</v>
       </c>
       <c r="R47" t="n">
-        <v>6822793</v>
+        <v>6822561</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5389,12 +5362,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5421,10 +5394,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117711960</v>
+        <v>117711997</v>
       </c>
       <c r="B48" t="n">
-        <v>78480</v>
+        <v>78127</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5437,21 +5410,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5461,10 +5434,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464895</v>
+        <v>464790</v>
       </c>
       <c r="R48" t="n">
-        <v>6822799</v>
+        <v>6822679</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5523,10 +5496,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117711939</v>
+        <v>117711840</v>
       </c>
       <c r="B49" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5563,10 +5536,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464944</v>
+        <v>464918</v>
       </c>
       <c r="R49" t="n">
-        <v>6822809</v>
+        <v>6822794</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5625,10 +5598,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117711938</v>
+        <v>117711500</v>
       </c>
       <c r="B50" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5641,21 +5614,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5665,10 +5638,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464956</v>
+        <v>464862</v>
       </c>
       <c r="R50" t="n">
-        <v>6822819</v>
+        <v>6822691</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5695,12 +5668,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5727,10 +5700,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117711411</v>
+        <v>117711755</v>
       </c>
       <c r="B51" t="n">
-        <v>78514</v>
+        <v>78482</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,21 +5716,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5767,10 +5740,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464887</v>
+        <v>464952</v>
       </c>
       <c r="R51" t="n">
-        <v>6822782</v>
+        <v>6822727</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5797,12 +5770,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5829,10 +5802,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117711999</v>
+        <v>117711589</v>
       </c>
       <c r="B52" t="n">
-        <v>78125</v>
+        <v>79467</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5841,25 +5814,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6456</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5869,10 +5842,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464823</v>
+        <v>464773</v>
       </c>
       <c r="R52" t="n">
-        <v>6822584</v>
+        <v>6822810</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5931,10 +5904,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117711942</v>
+        <v>117711556</v>
       </c>
       <c r="B53" t="n">
-        <v>78480</v>
+        <v>79592</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5943,38 +5916,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464917</v>
+        <v>464979</v>
       </c>
       <c r="R53" t="n">
-        <v>6822797</v>
+        <v>6822661</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6009,12 +5985,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6033,10 +6015,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117711755</v>
+        <v>117711753</v>
       </c>
       <c r="B54" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6073,10 +6055,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464952</v>
+        <v>464957</v>
       </c>
       <c r="R54" t="n">
-        <v>6822727</v>
+        <v>6822668</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6135,10 +6117,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117711500</v>
+        <v>117711514</v>
       </c>
       <c r="B55" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6175,10 +6157,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464862</v>
+        <v>464789</v>
       </c>
       <c r="R55" t="n">
-        <v>6822691</v>
+        <v>6822646</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6237,10 +6219,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117711670</v>
+        <v>117711757</v>
       </c>
       <c r="B56" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6253,21 +6235,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6277,10 +6259,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464796</v>
+        <v>464957</v>
       </c>
       <c r="R56" t="n">
-        <v>6822550</v>
+        <v>6822685</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6307,12 +6289,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6339,10 +6321,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117711968</v>
+        <v>117711957</v>
       </c>
       <c r="B57" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6379,10 +6361,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464845</v>
+        <v>464891</v>
       </c>
       <c r="R57" t="n">
-        <v>6822867</v>
+        <v>6822781</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6441,10 +6423,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117711556</v>
+        <v>117711496</v>
       </c>
       <c r="B58" t="n">
-        <v>79590</v>
+        <v>79100</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6453,41 +6435,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464979</v>
+        <v>464827</v>
       </c>
       <c r="R58" t="n">
-        <v>6822661</v>
+        <v>6822493</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6514,17 +6493,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6533,7 +6507,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6552,10 +6525,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117711719</v>
+        <v>117711751</v>
       </c>
       <c r="B59" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6568,21 +6541,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6592,10 +6565,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464779</v>
+        <v>465064</v>
       </c>
       <c r="R59" t="n">
-        <v>6822837</v>
+        <v>6822518</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6622,12 +6595,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6654,10 +6627,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117711613</v>
+        <v>117711513</v>
       </c>
       <c r="B60" t="n">
-        <v>78506</v>
+        <v>79100</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6666,25 +6639,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6694,10 +6667,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464776</v>
+        <v>464787</v>
       </c>
       <c r="R60" t="n">
-        <v>6822609</v>
+        <v>6822645</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6756,10 +6729,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117711509</v>
+        <v>117711667</v>
       </c>
       <c r="B61" t="n">
-        <v>79098</v>
+        <v>78219</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6772,21 +6745,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6796,10 +6769,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464812</v>
+        <v>464785</v>
       </c>
       <c r="R61" t="n">
-        <v>6822825</v>
+        <v>6822821</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6858,10 +6831,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117711415</v>
+        <v>117711526</v>
       </c>
       <c r="B62" t="n">
-        <v>78514</v>
+        <v>79071</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6874,21 +6847,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6898,10 +6871,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464750</v>
+        <v>464802</v>
       </c>
       <c r="R62" t="n">
-        <v>6822791</v>
+        <v>6822558</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6960,10 +6933,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117711937</v>
+        <v>117711558</v>
       </c>
       <c r="B63" t="n">
-        <v>78480</v>
+        <v>79592</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6972,38 +6945,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464940</v>
+        <v>465071</v>
       </c>
       <c r="R63" t="n">
-        <v>6822856</v>
+        <v>6822559</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7038,12 +7014,18 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7062,10 +7044,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117711749</v>
+        <v>117711964</v>
       </c>
       <c r="B64" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7102,10 +7084,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>465020</v>
+        <v>464854</v>
       </c>
       <c r="R64" t="n">
-        <v>6822478</v>
+        <v>6822833</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7132,12 +7114,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7164,10 +7146,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117711750</v>
+        <v>117711982</v>
       </c>
       <c r="B65" t="n">
-        <v>78480</v>
+        <v>94505</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7176,25 +7158,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7204,10 +7186,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>465035</v>
+        <v>464829</v>
       </c>
       <c r="R65" t="n">
-        <v>6822499</v>
+        <v>6822608</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7234,12 +7216,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7266,10 +7248,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117711570</v>
+        <v>117711943</v>
       </c>
       <c r="B66" t="n">
-        <v>79590</v>
+        <v>78482</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7278,41 +7260,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464946</v>
+        <v>464914</v>
       </c>
       <c r="R66" t="n">
-        <v>6822832</v>
+        <v>6822793</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7347,18 +7326,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7377,10 +7350,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117711513</v>
+        <v>117711519</v>
       </c>
       <c r="B67" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7417,10 +7390,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464787</v>
+        <v>464829</v>
       </c>
       <c r="R67" t="n">
-        <v>6822645</v>
+        <v>6822493</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7479,10 +7452,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117711694</v>
+        <v>117711956</v>
       </c>
       <c r="B68" t="n">
-        <v>78216</v>
+        <v>78482</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7495,21 +7468,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7519,10 +7492,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>465016</v>
+        <v>464884</v>
       </c>
       <c r="R68" t="n">
-        <v>6822483</v>
+        <v>6822771</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7549,12 +7522,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7581,10 +7554,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117711515</v>
+        <v>117711508</v>
       </c>
       <c r="B69" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7621,10 +7594,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464791</v>
+        <v>464807</v>
       </c>
       <c r="R69" t="n">
-        <v>6822636</v>
+        <v>6822845</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7683,10 +7656,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117711622</v>
+        <v>117711573</v>
       </c>
       <c r="B70" t="n">
-        <v>79589</v>
+        <v>79592</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7699,34 +7672,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464806</v>
+        <v>464830</v>
       </c>
       <c r="R70" t="n">
-        <v>6822865</v>
+        <v>6822871</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7761,12 +7737,18 @@
           <t>2024-06-09</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7785,10 +7767,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117711953</v>
+        <v>117711724</v>
       </c>
       <c r="B71" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7801,21 +7783,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7825,10 +7807,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464900</v>
+        <v>464829</v>
       </c>
       <c r="R71" t="n">
-        <v>6822625</v>
+        <v>6822493</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7887,10 +7869,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117711954</v>
+        <v>117711412</v>
       </c>
       <c r="B72" t="n">
-        <v>78480</v>
+        <v>78516</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7903,21 +7885,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7927,10 +7909,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>464919</v>
+        <v>464821</v>
       </c>
       <c r="R72" t="n">
-        <v>6822626</v>
+        <v>6822795</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7989,10 +7971,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117711663</v>
+        <v>117711999</v>
       </c>
       <c r="B73" t="n">
-        <v>78217</v>
+        <v>78127</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8005,21 +7987,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8029,7 +8011,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464857</v>
+        <v>464823</v>
       </c>
       <c r="R73" t="n">
         <v>6822584</v>
@@ -8091,10 +8073,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117711965</v>
+        <v>117711756</v>
       </c>
       <c r="B74" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8131,10 +8113,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>464847</v>
+        <v>464963</v>
       </c>
       <c r="R74" t="n">
-        <v>6822842</v>
+        <v>6822708</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8161,12 +8143,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8193,10 +8175,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117711955</v>
+        <v>117711938</v>
       </c>
       <c r="B75" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8233,10 +8215,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464884</v>
+        <v>464956</v>
       </c>
       <c r="R75" t="n">
-        <v>6822736</v>
+        <v>6822819</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8263,12 +8245,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8295,10 +8277,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117711671</v>
+        <v>117711578</v>
       </c>
       <c r="B76" t="n">
-        <v>78217</v>
+        <v>57304</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8311,34 +8293,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464829</v>
+        <v>464962</v>
       </c>
       <c r="R76" t="n">
-        <v>6822493</v>
+        <v>6822707</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8365,12 +8355,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8397,10 +8387,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117711508</v>
+        <v>117711378</v>
       </c>
       <c r="B77" t="n">
-        <v>79098</v>
+        <v>5186</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8409,38 +8399,47 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>105930</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>464807</v>
+        <v>465023</v>
       </c>
       <c r="R77" t="n">
-        <v>6822845</v>
+        <v>6822630</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8467,12 +8466,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8481,6 +8480,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8499,10 +8499,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117711499</v>
+        <v>117711663</v>
       </c>
       <c r="B78" t="n">
-        <v>79098</v>
+        <v>78219</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8515,21 +8515,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8539,10 +8539,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464873</v>
+        <v>464857</v>
       </c>
       <c r="R78" t="n">
-        <v>6822661</v>
+        <v>6822584</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8601,10 +8601,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117711497</v>
+        <v>117711664</v>
       </c>
       <c r="B79" t="n">
-        <v>79098</v>
+        <v>78219</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8617,21 +8617,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8641,10 +8641,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464842</v>
+        <v>464835</v>
       </c>
       <c r="R79" t="n">
-        <v>6822509</v>
+        <v>6822696</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8703,10 +8703,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117711997</v>
+        <v>117711962</v>
       </c>
       <c r="B80" t="n">
-        <v>78125</v>
+        <v>78482</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8719,21 +8719,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>464790</v>
+        <v>464870</v>
       </c>
       <c r="R80" t="n">
-        <v>6822679</v>
+        <v>6822808</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8805,10 +8805,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117711757</v>
+        <v>117711613</v>
       </c>
       <c r="B81" t="n">
-        <v>78480</v>
+        <v>78508</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8817,25 +8817,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8845,10 +8845,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464957</v>
+        <v>464776</v>
       </c>
       <c r="R81" t="n">
-        <v>6822685</v>
+        <v>6822609</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8875,12 +8875,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8907,10 +8907,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117711514</v>
+        <v>117711622</v>
       </c>
       <c r="B82" t="n">
-        <v>79098</v>
+        <v>79591</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8919,25 +8919,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6461</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8947,10 +8947,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464789</v>
+        <v>464806</v>
       </c>
       <c r="R82" t="n">
-        <v>6822646</v>
+        <v>6822865</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9009,10 +9009,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117711516</v>
+        <v>117711968</v>
       </c>
       <c r="B83" t="n">
-        <v>79098</v>
+        <v>78482</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9025,21 +9025,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9049,10 +9049,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464802</v>
+        <v>464845</v>
       </c>
       <c r="R83" t="n">
-        <v>6822558</v>
+        <v>6822867</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9111,10 +9111,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117712000</v>
+        <v>117711498</v>
       </c>
       <c r="B84" t="n">
-        <v>78125</v>
+        <v>79100</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9127,21 +9127,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9151,10 +9151,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464806</v>
+        <v>464862</v>
       </c>
       <c r="R84" t="n">
-        <v>6822556</v>
+        <v>6822596</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9213,10 +9213,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117711962</v>
+        <v>117711998</v>
       </c>
       <c r="B85" t="n">
-        <v>78480</v>
+        <v>78127</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9229,21 +9229,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9253,10 +9253,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464870</v>
+        <v>464781</v>
       </c>
       <c r="R85" t="n">
-        <v>6822808</v>
+        <v>6822679</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9315,10 +9315,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117711840</v>
+        <v>117711614</v>
       </c>
       <c r="B86" t="n">
-        <v>78480</v>
+        <v>78508</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9327,25 +9327,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464918</v>
+        <v>464794</v>
       </c>
       <c r="R86" t="n">
-        <v>6822794</v>
+        <v>6822546</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9385,12 +9385,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9417,10 +9417,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117711961</v>
+        <v>117711515</v>
       </c>
       <c r="B87" t="n">
-        <v>78480</v>
+        <v>79100</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9433,21 +9433,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9457,10 +9457,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>464869</v>
+        <v>464791</v>
       </c>
       <c r="R87" t="n">
-        <v>6822820</v>
+        <v>6822636</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9519,10 +9519,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117711518</v>
+        <v>117711722</v>
       </c>
       <c r="B88" t="n">
-        <v>79098</v>
+        <v>78218</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9535,21 +9535,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9559,10 +9559,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464788</v>
+        <v>464796</v>
       </c>
       <c r="R88" t="n">
-        <v>6822536</v>
+        <v>6822550</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9621,10 +9621,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117711589</v>
+        <v>117711516</v>
       </c>
       <c r="B89" t="n">
-        <v>79465</v>
+        <v>79100</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9633,25 +9633,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464773</v>
+        <v>464802</v>
       </c>
       <c r="R89" t="n">
-        <v>6822810</v>
+        <v>6822558</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9723,10 +9723,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117711668</v>
+        <v>117711955</v>
       </c>
       <c r="B90" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9739,21 +9739,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9763,10 +9763,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464814</v>
+        <v>464884</v>
       </c>
       <c r="R90" t="n">
-        <v>6822561</v>
+        <v>6822736</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 47905-2023 artfynd.xlsx
+++ b/artfynd/A 47905-2023 artfynd.xlsx
@@ -2316,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117711504</v>
+        <v>117711670</v>
       </c>
       <c r="B18" t="n">
-        <v>79100</v>
+        <v>78219</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2332,21 +2332,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464812</v>
+        <v>464796</v>
       </c>
       <c r="R18" t="n">
-        <v>6822865</v>
+        <v>6822550</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117711750</v>
+        <v>117711504</v>
       </c>
       <c r="B19" t="n">
-        <v>78482</v>
+        <v>79100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465035</v>
+        <v>464812</v>
       </c>
       <c r="R19" t="n">
-        <v>6822499</v>
+        <v>6822865</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2488,12 +2488,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2520,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711512</v>
+        <v>117711750</v>
       </c>
       <c r="B20" t="n">
-        <v>79100</v>
+        <v>78482</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2536,21 +2536,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464797</v>
+        <v>465035</v>
       </c>
       <c r="R20" t="n">
-        <v>6822693</v>
+        <v>6822499</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2622,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117711719</v>
+        <v>117711512</v>
       </c>
       <c r="B21" t="n">
-        <v>78218</v>
+        <v>79100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2638,21 +2638,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464779</v>
+        <v>464797</v>
       </c>
       <c r="R21" t="n">
-        <v>6822837</v>
+        <v>6822693</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117711961</v>
+        <v>117711719</v>
       </c>
       <c r="B22" t="n">
-        <v>78482</v>
+        <v>78218</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464869</v>
+        <v>464779</v>
       </c>
       <c r="R22" t="n">
-        <v>6822820</v>
+        <v>6822837</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117711670</v>
+        <v>117711961</v>
       </c>
       <c r="B23" t="n">
-        <v>78219</v>
+        <v>78482</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2842,21 +2842,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464796</v>
+        <v>464869</v>
       </c>
       <c r="R23" t="n">
-        <v>6822550</v>
+        <v>6822820</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -5598,10 +5598,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117711500</v>
+        <v>117711753</v>
       </c>
       <c r="B50" t="n">
-        <v>79100</v>
+        <v>78482</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5614,21 +5614,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>464862</v>
+        <v>464957</v>
       </c>
       <c r="R50" t="n">
-        <v>6822691</v>
+        <v>6822668</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5668,12 +5668,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5700,10 +5700,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117711755</v>
+        <v>117711514</v>
       </c>
       <c r="B51" t="n">
-        <v>78482</v>
+        <v>79100</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5716,21 +5716,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464952</v>
+        <v>464789</v>
       </c>
       <c r="R51" t="n">
-        <v>6822727</v>
+        <v>6822646</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5802,10 +5802,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117711589</v>
+        <v>117711500</v>
       </c>
       <c r="B52" t="n">
-        <v>79467</v>
+        <v>79100</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5814,25 +5814,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464773</v>
+        <v>464862</v>
       </c>
       <c r="R52" t="n">
-        <v>6822810</v>
+        <v>6822691</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117711556</v>
+        <v>117711755</v>
       </c>
       <c r="B53" t="n">
-        <v>79592</v>
+        <v>78482</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5916,41 +5916,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464979</v>
+        <v>464952</v>
       </c>
       <c r="R53" t="n">
-        <v>6822661</v>
+        <v>6822727</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5985,18 +5982,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6015,10 +6006,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117711753</v>
+        <v>117711589</v>
       </c>
       <c r="B54" t="n">
-        <v>78482</v>
+        <v>79467</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6027,25 +6018,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6055,10 +6046,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464957</v>
+        <v>464773</v>
       </c>
       <c r="R54" t="n">
-        <v>6822668</v>
+        <v>6822810</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6085,12 +6076,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6117,10 +6108,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117711514</v>
+        <v>117711556</v>
       </c>
       <c r="B55" t="n">
-        <v>79100</v>
+        <v>79592</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6129,38 +6120,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464789</v>
+        <v>464979</v>
       </c>
       <c r="R55" t="n">
-        <v>6822646</v>
+        <v>6822661</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6187,12 +6181,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6201,6 +6200,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6831,10 +6831,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117711526</v>
+        <v>117711982</v>
       </c>
       <c r="B62" t="n">
-        <v>79071</v>
+        <v>94505</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6843,25 +6843,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>2170</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464802</v>
+        <v>464829</v>
       </c>
       <c r="R62" t="n">
-        <v>6822558</v>
+        <v>6822608</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7146,10 +7146,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117711982</v>
+        <v>117711526</v>
       </c>
       <c r="B65" t="n">
-        <v>94505</v>
+        <v>79071</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7158,25 +7158,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2170</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464829</v>
+        <v>464802</v>
       </c>
       <c r="R65" t="n">
-        <v>6822608</v>
+        <v>6822558</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 47905-2023 artfynd.xlsx
+++ b/artfynd/A 47905-2023 artfynd.xlsx
@@ -9825,10 +9825,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119549078</v>
+        <v>119549063</v>
       </c>
       <c r="B91" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9841,26 +9841,26 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9874,10 +9874,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464804</v>
+        <v>464809</v>
       </c>
       <c r="R91" t="n">
-        <v>6822584</v>
+        <v>6822528</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9936,10 +9936,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119549058</v>
+        <v>119549078</v>
       </c>
       <c r="B92" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9948,38 +9948,47 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464949</v>
+        <v>464804</v>
       </c>
       <c r="R92" t="n">
-        <v>6822470</v>
+        <v>6822584</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10038,10 +10047,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119549083</v>
+        <v>119549058</v>
       </c>
       <c r="B93" t="n">
-        <v>77910</v>
+        <v>79144</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10054,21 +10063,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10078,10 +10087,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>465017</v>
+        <v>464949</v>
       </c>
       <c r="R93" t="n">
-        <v>6822483</v>
+        <v>6822470</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10140,10 +10149,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119549063</v>
+        <v>119549083</v>
       </c>
       <c r="B94" t="n">
-        <v>91852</v>
+        <v>77910</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10152,47 +10161,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4366</v>
+        <v>6437</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464809</v>
+        <v>465017</v>
       </c>
       <c r="R94" t="n">
-        <v>6822528</v>
+        <v>6822483</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>

--- a/artfynd/A 47905-2023 artfynd.xlsx
+++ b/artfynd/A 47905-2023 artfynd.xlsx
@@ -9936,10 +9936,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119549078</v>
+        <v>119549083</v>
       </c>
       <c r="B92" t="n">
-        <v>91840</v>
+        <v>77910</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -9948,47 +9948,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>464804</v>
+        <v>465017</v>
       </c>
       <c r="R92" t="n">
-        <v>6822584</v>
+        <v>6822483</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10047,10 +10038,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119549058</v>
+        <v>119549078</v>
       </c>
       <c r="B93" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10059,38 +10050,47 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464949</v>
+        <v>464804</v>
       </c>
       <c r="R93" t="n">
-        <v>6822470</v>
+        <v>6822584</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10149,10 +10149,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119549083</v>
+        <v>119549058</v>
       </c>
       <c r="B94" t="n">
-        <v>77910</v>
+        <v>79144</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10165,21 +10165,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10189,10 +10189,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>465017</v>
+        <v>464949</v>
       </c>
       <c r="R94" t="n">
-        <v>6822483</v>
+        <v>6822470</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>

--- a/artfynd/A 47905-2023 artfynd.xlsx
+++ b/artfynd/A 47905-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117711937</v>
+        <v>117711529</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>464940</v>
+        <v>464772</v>
       </c>
       <c r="R2" t="n">
-        <v>6822856</v>
+        <v>6822599</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117711953</v>
+        <v>117711411</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>464900</v>
+        <v>464887</v>
       </c>
       <c r="R3" t="n">
-        <v>6822625</v>
+        <v>6822782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117711956</v>
+        <v>117711412</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>464884</v>
+        <v>464821</v>
       </c>
       <c r="R4" t="n">
-        <v>6822771</v>
+        <v>6822795</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117711495</v>
+        <v>117711413</v>
       </c>
       <c r="B5" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>464963</v>
+        <v>464796</v>
       </c>
       <c r="R5" t="n">
-        <v>6822863</v>
+        <v>6822812</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117711413</v>
+        <v>117711415</v>
       </c>
       <c r="B6" t="n">
-        <v>78518</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>464796</v>
+        <v>464750</v>
       </c>
       <c r="R6" t="n">
-        <v>6822812</v>
+        <v>6822791</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117711933</v>
+        <v>117711996</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>464953</v>
+        <v>464737</v>
       </c>
       <c r="R7" t="n">
-        <v>6822873</v>
+        <v>6822864</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117711938</v>
+        <v>117711997</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464956</v>
+        <v>464790</v>
       </c>
       <c r="R8" t="n">
-        <v>6822819</v>
+        <v>6822679</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117711589</v>
+        <v>117711998</v>
       </c>
       <c r="B9" t="n">
-        <v>79469</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>464773</v>
+        <v>464781</v>
       </c>
       <c r="R9" t="n">
-        <v>6822810</v>
+        <v>6822679</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117711509</v>
+        <v>117711999</v>
       </c>
       <c r="B10" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>464812</v>
+        <v>464823</v>
       </c>
       <c r="R10" t="n">
-        <v>6822825</v>
+        <v>6822584</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117711959</v>
+        <v>117712000</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>464897</v>
+        <v>464806</v>
       </c>
       <c r="R11" t="n">
-        <v>6822794</v>
+        <v>6822556</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117711957</v>
+        <v>117711982</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>464891</v>
+        <v>464829</v>
       </c>
       <c r="R12" t="n">
-        <v>6822781</v>
+        <v>6822608</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117711512</v>
+        <v>119549078</v>
       </c>
       <c r="B13" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1813,34 +1753,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>464797</v>
+        <v>464804</v>
       </c>
       <c r="R13" t="n">
-        <v>6822693</v>
+        <v>6822584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,12 +1816,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1899,15 +1848,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117711718</v>
+        <v>119549062</v>
       </c>
       <c r="B14" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1915,34 +1859,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>464807</v>
+        <v>464824</v>
       </c>
       <c r="R14" t="n">
-        <v>6822845</v>
+        <v>6822456</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,12 +1922,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,15 +1954,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117711502</v>
+        <v>119549063</v>
       </c>
       <c r="B15" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2017,34 +1965,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>464832</v>
+        <v>464809</v>
       </c>
       <c r="R15" t="n">
-        <v>6822695</v>
+        <v>6822528</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,12 +2028,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,19 +2060,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117711939</v>
+        <v>117711748</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2143,10 +2095,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>464944</v>
+        <v>465080</v>
       </c>
       <c r="R16" t="n">
-        <v>6822809</v>
+        <v>6822501</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,19 +2157,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117711751</v>
+        <v>117711749</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2245,10 +2192,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>465064</v>
+        <v>465020</v>
       </c>
       <c r="R17" t="n">
-        <v>6822518</v>
+        <v>6822478</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,37 +2254,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117711668</v>
+        <v>117711750</v>
       </c>
       <c r="B18" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2289,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>464814</v>
+        <v>465035</v>
       </c>
       <c r="R18" t="n">
-        <v>6822561</v>
+        <v>6822499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,12 +2319,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2409,59 +2351,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117711378</v>
+        <v>117711751</v>
       </c>
       <c r="B19" t="n">
-        <v>5186</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>465023</v>
+        <v>465064</v>
       </c>
       <c r="R19" t="n">
-        <v>6822630</v>
+        <v>6822518</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,7 +2430,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2521,37 +2448,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117711412</v>
+        <v>117711752</v>
       </c>
       <c r="B20" t="n">
-        <v>78518</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2561,10 +2483,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464821</v>
+        <v>464991</v>
       </c>
       <c r="R20" t="n">
-        <v>6822795</v>
+        <v>6822675</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,12 +2513,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2623,37 +2545,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117711515</v>
+        <v>117711753</v>
       </c>
       <c r="B21" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2580,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464791</v>
+        <v>464957</v>
       </c>
       <c r="R21" t="n">
-        <v>6822636</v>
+        <v>6822668</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2693,12 +2610,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2725,37 +2642,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117711510</v>
+        <v>117711755</v>
       </c>
       <c r="B22" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2765,10 +2677,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464779</v>
+        <v>464952</v>
       </c>
       <c r="R22" t="n">
-        <v>6822835</v>
+        <v>6822727</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2795,12 +2707,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2827,37 +2739,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117712000</v>
+        <v>117711756</v>
       </c>
       <c r="B23" t="n">
-        <v>78129</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2867,10 +2774,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>464806</v>
+        <v>464963</v>
       </c>
       <c r="R23" t="n">
-        <v>6822556</v>
+        <v>6822708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2897,12 +2804,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2929,19 +2836,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117711759</v>
+        <v>117711757</v>
       </c>
       <c r="B24" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2969,10 +2871,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>465025</v>
+        <v>464957</v>
       </c>
       <c r="R24" t="n">
-        <v>6822630</v>
+        <v>6822685</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3031,19 +2933,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117711972</v>
+        <v>117711759</v>
       </c>
       <c r="B25" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3071,10 +2968,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>464787</v>
+        <v>465025</v>
       </c>
       <c r="R25" t="n">
-        <v>6822809</v>
+        <v>6822630</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3101,12 +2998,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3133,37 +3030,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117711519</v>
+        <v>117711761</v>
       </c>
       <c r="B26" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3173,10 +3065,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>464829</v>
+        <v>465039</v>
       </c>
       <c r="R26" t="n">
-        <v>6822493</v>
+        <v>6822657</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3203,12 +3095,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3235,37 +3127,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117711514</v>
+        <v>117711762</v>
       </c>
       <c r="B27" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3275,10 +3162,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>464789</v>
+        <v>465053</v>
       </c>
       <c r="R27" t="n">
-        <v>6822646</v>
+        <v>6822667</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3305,12 +3192,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3337,37 +3224,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117711500</v>
+        <v>117711763</v>
       </c>
       <c r="B28" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3377,10 +3259,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>464862</v>
+        <v>465048</v>
       </c>
       <c r="R28" t="n">
-        <v>6822691</v>
+        <v>6822660</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3407,12 +3289,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3439,37 +3321,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117711613</v>
+        <v>117711839</v>
       </c>
       <c r="B29" t="n">
-        <v>78510</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3479,10 +3356,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>464776</v>
+        <v>464908</v>
       </c>
       <c r="R29" t="n">
-        <v>6822609</v>
+        <v>6822788</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3509,12 +3386,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3541,37 +3418,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117711663</v>
+        <v>117711840</v>
       </c>
       <c r="B30" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3581,10 +3453,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>464857</v>
+        <v>464918</v>
       </c>
       <c r="R30" t="n">
-        <v>6822584</v>
+        <v>6822794</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3611,12 +3483,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3643,19 +3515,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117711756</v>
+        <v>117711907</v>
       </c>
       <c r="B31" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3683,10 +3550,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>464963</v>
+        <v>465022</v>
       </c>
       <c r="R31" t="n">
-        <v>6822708</v>
+        <v>6822851</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3745,19 +3612,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117711932</v>
+        <v>117711929</v>
       </c>
       <c r="B32" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3785,10 +3647,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>464956</v>
+        <v>464985</v>
       </c>
       <c r="R32" t="n">
-        <v>6822869</v>
+        <v>6822805</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3847,19 +3709,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117711944</v>
+        <v>117711930</v>
       </c>
       <c r="B33" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3887,10 +3744,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>464915</v>
+        <v>464991</v>
       </c>
       <c r="R33" t="n">
-        <v>6822788</v>
+        <v>6822809</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3949,37 +3806,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117711497</v>
+        <v>117711931</v>
       </c>
       <c r="B34" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3989,10 +3841,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>464842</v>
+        <v>464993</v>
       </c>
       <c r="R34" t="n">
-        <v>6822509</v>
+        <v>6822829</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4019,12 +3871,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4051,19 +3903,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117711942</v>
+        <v>117711932</v>
       </c>
       <c r="B35" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4091,10 +3938,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>464917</v>
+        <v>464956</v>
       </c>
       <c r="R35" t="n">
-        <v>6822797</v>
+        <v>6822869</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4153,19 +4000,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117711960</v>
+        <v>117711933</v>
       </c>
       <c r="B36" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4193,10 +4035,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>464895</v>
+        <v>464953</v>
       </c>
       <c r="R36" t="n">
-        <v>6822799</v>
+        <v>6822873</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4223,12 +4065,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4255,19 +4097,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117711965</v>
+        <v>117711934</v>
       </c>
       <c r="B37" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4295,10 +4132,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>464847</v>
+        <v>464938</v>
       </c>
       <c r="R37" t="n">
-        <v>6822842</v>
+        <v>6822884</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4325,12 +4162,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4357,58 +4194,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117711578</v>
+        <v>117711935</v>
       </c>
       <c r="B38" t="n">
-        <v>57306</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>464962</v>
+        <v>464911</v>
       </c>
       <c r="R38" t="n">
-        <v>6822707</v>
+        <v>6822873</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4467,37 +4291,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117711997</v>
+        <v>117711936</v>
       </c>
       <c r="B39" t="n">
-        <v>78129</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4507,10 +4326,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>464790</v>
+        <v>464914</v>
       </c>
       <c r="R39" t="n">
-        <v>6822679</v>
+        <v>6822863</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4537,12 +4356,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4569,19 +4388,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117711753</v>
+        <v>117711937</v>
       </c>
       <c r="B40" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4609,10 +4423,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>464957</v>
+        <v>464940</v>
       </c>
       <c r="R40" t="n">
-        <v>6822668</v>
+        <v>6822856</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4671,37 +4485,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117711724</v>
+        <v>117711938</v>
       </c>
       <c r="B41" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4711,10 +4520,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>464829</v>
+        <v>464956</v>
       </c>
       <c r="R41" t="n">
-        <v>6822493</v>
+        <v>6822819</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4741,12 +4550,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4773,37 +4582,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117711998</v>
+        <v>117711939</v>
       </c>
       <c r="B42" t="n">
-        <v>78129</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4813,10 +4617,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>464781</v>
+        <v>464944</v>
       </c>
       <c r="R42" t="n">
-        <v>6822679</v>
+        <v>6822809</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4843,12 +4647,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4875,37 +4679,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117711695</v>
+        <v>117711940</v>
       </c>
       <c r="B43" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4915,10 +4714,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>464953</v>
+        <v>464930</v>
       </c>
       <c r="R43" t="n">
-        <v>6822673</v>
+        <v>6822763</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4977,19 +4776,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117711943</v>
+        <v>117711941</v>
       </c>
       <c r="B44" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5017,10 +4811,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>464914</v>
+        <v>464929</v>
       </c>
       <c r="R44" t="n">
-        <v>6822793</v>
+        <v>6822784</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5079,37 +4873,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117711671</v>
+        <v>117711942</v>
       </c>
       <c r="B45" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5119,10 +4908,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>464829</v>
+        <v>464917</v>
       </c>
       <c r="R45" t="n">
-        <v>6822493</v>
+        <v>6822797</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5149,12 +4938,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5181,37 +4970,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117711721</v>
+        <v>117711943</v>
       </c>
       <c r="B46" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5221,10 +5005,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>464811</v>
+        <v>464914</v>
       </c>
       <c r="R46" t="n">
-        <v>6822558</v>
+        <v>6822793</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5251,12 +5035,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5283,19 +5067,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117711961</v>
+        <v>117711944</v>
       </c>
       <c r="B47" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5323,10 +5102,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>464869</v>
+        <v>464915</v>
       </c>
       <c r="R47" t="n">
-        <v>6822820</v>
+        <v>6822788</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5353,12 +5132,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5385,19 +5164,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117711968</v>
+        <v>117711947</v>
       </c>
       <c r="B48" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5425,10 +5199,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>464845</v>
+        <v>464785</v>
       </c>
       <c r="R48" t="n">
-        <v>6822867</v>
+        <v>6822458</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5487,37 +5261,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117711621</v>
+        <v>117711948</v>
       </c>
       <c r="B49" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5527,10 +5296,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>464960</v>
+        <v>464796</v>
       </c>
       <c r="R49" t="n">
-        <v>6822857</v>
+        <v>6822455</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5557,12 +5326,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5589,53 +5358,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117711559</v>
+        <v>117711950</v>
       </c>
       <c r="B50" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>465044</v>
+        <v>464809</v>
       </c>
       <c r="R50" t="n">
-        <v>6822619</v>
+        <v>6822459</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5662,17 +5423,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5681,7 +5437,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5700,37 +5455,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117711722</v>
+        <v>117711952</v>
       </c>
       <c r="B51" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5740,10 +5490,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>464796</v>
+        <v>464849</v>
       </c>
       <c r="R51" t="n">
-        <v>6822550</v>
+        <v>6822503</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5802,37 +5552,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117711664</v>
+        <v>117711953</v>
       </c>
       <c r="B52" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5842,10 +5587,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>464835</v>
+        <v>464900</v>
       </c>
       <c r="R52" t="n">
-        <v>6822696</v>
+        <v>6822625</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5904,37 +5649,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117711415</v>
+        <v>117711954</v>
       </c>
       <c r="B53" t="n">
-        <v>78518</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5944,10 +5684,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>464750</v>
+        <v>464919</v>
       </c>
       <c r="R53" t="n">
-        <v>6822791</v>
+        <v>6822626</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6006,37 +5746,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117711999</v>
+        <v>117711955</v>
       </c>
       <c r="B54" t="n">
-        <v>78129</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6046,10 +5781,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>464823</v>
+        <v>464884</v>
       </c>
       <c r="R54" t="n">
-        <v>6822584</v>
+        <v>6822736</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6108,19 +5843,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117711962</v>
+        <v>117711956</v>
       </c>
       <c r="B55" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6148,10 +5878,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>464870</v>
+        <v>464884</v>
       </c>
       <c r="R55" t="n">
-        <v>6822808</v>
+        <v>6822771</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6210,37 +5940,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117711496</v>
+        <v>117711957</v>
       </c>
       <c r="B56" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6250,10 +5975,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>464827</v>
+        <v>464891</v>
       </c>
       <c r="R56" t="n">
-        <v>6822493</v>
+        <v>6822781</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6312,37 +6037,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117711617</v>
+        <v>117711959</v>
       </c>
       <c r="B57" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6352,10 +6072,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>464933</v>
+        <v>464897</v>
       </c>
       <c r="R57" t="n">
-        <v>6822795</v>
+        <v>6822794</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6382,12 +6102,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6414,19 +6134,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117711964</v>
+        <v>117711960</v>
       </c>
       <c r="B58" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -6454,10 +6169,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>464854</v>
+        <v>464895</v>
       </c>
       <c r="R58" t="n">
-        <v>6822833</v>
+        <v>6822799</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6516,19 +6231,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117711955</v>
+        <v>117711961</v>
       </c>
       <c r="B59" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6556,10 +6266,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>464884</v>
+        <v>464869</v>
       </c>
       <c r="R59" t="n">
-        <v>6822736</v>
+        <v>6822820</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6618,19 +6328,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117711954</v>
+        <v>117711962</v>
       </c>
       <c r="B60" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -6658,10 +6363,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>464919</v>
+        <v>464870</v>
       </c>
       <c r="R60" t="n">
-        <v>6822626</v>
+        <v>6822808</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6720,37 +6425,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117711508</v>
+        <v>117711963</v>
       </c>
       <c r="B61" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6760,10 +6460,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>464807</v>
+        <v>464863</v>
       </c>
       <c r="R61" t="n">
-        <v>6822845</v>
+        <v>6822841</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6822,37 +6522,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117711504</v>
+        <v>117711964</v>
       </c>
       <c r="B62" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6862,10 +6557,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>464812</v>
+        <v>464854</v>
       </c>
       <c r="R62" t="n">
-        <v>6822865</v>
+        <v>6822833</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6924,37 +6619,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117711723</v>
+        <v>117711965</v>
       </c>
       <c r="B63" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6964,10 +6654,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>464798</v>
+        <v>464847</v>
       </c>
       <c r="R63" t="n">
-        <v>6822515</v>
+        <v>6822842</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7026,37 +6716,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117711498</v>
+        <v>117711966</v>
       </c>
       <c r="B64" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7066,10 +6751,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>464862</v>
+        <v>464860</v>
       </c>
       <c r="R64" t="n">
-        <v>6822596</v>
+        <v>6822861</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7128,37 +6813,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117711526</v>
+        <v>117711967</v>
       </c>
       <c r="B65" t="n">
-        <v>79073</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7168,10 +6848,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>464802</v>
+        <v>464861</v>
       </c>
       <c r="R65" t="n">
-        <v>6822558</v>
+        <v>6822867</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7230,37 +6910,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117711670</v>
+        <v>117711968</v>
       </c>
       <c r="B66" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7270,10 +6945,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>464796</v>
+        <v>464845</v>
       </c>
       <c r="R66" t="n">
-        <v>6822550</v>
+        <v>6822867</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7332,53 +7007,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117711570</v>
+        <v>117711969</v>
       </c>
       <c r="B67" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>464946</v>
+        <v>464707</v>
       </c>
       <c r="R67" t="n">
-        <v>6822832</v>
+        <v>6822857</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7405,17 +7072,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7424,7 +7086,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7443,53 +7104,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117711556</v>
+        <v>117711972</v>
       </c>
       <c r="B68" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>464979</v>
+        <v>464787</v>
       </c>
       <c r="R68" t="n">
-        <v>6822661</v>
+        <v>6822809</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7516,17 +7169,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7535,7 +7183,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7554,37 +7201,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117711411</v>
+        <v>117711613</v>
       </c>
       <c r="B69" t="n">
-        <v>78518</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7594,10 +7236,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>464887</v>
+        <v>464776</v>
       </c>
       <c r="R69" t="n">
-        <v>6822782</v>
+        <v>6822609</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7656,37 +7298,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117711839</v>
+        <v>117711614</v>
       </c>
       <c r="B70" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7696,10 +7333,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>464908</v>
+        <v>464794</v>
       </c>
       <c r="R70" t="n">
-        <v>6822788</v>
+        <v>6822546</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7726,12 +7363,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7758,53 +7395,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117711561</v>
+        <v>119549083</v>
       </c>
       <c r="B71" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>464971</v>
+        <v>465017</v>
       </c>
       <c r="R71" t="n">
-        <v>6822628</v>
+        <v>6822483</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7831,17 +7460,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7850,7 +7474,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7869,53 +7492,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117711558</v>
+        <v>117711694</v>
       </c>
       <c r="B72" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>465071</v>
+        <v>465016</v>
       </c>
       <c r="R72" t="n">
-        <v>6822559</v>
+        <v>6822483</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7950,18 +7565,12 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7980,15 +7589,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117711518</v>
+        <v>117711695</v>
       </c>
       <c r="B73" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7996,21 +7600,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8020,10 +7624,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>464788</v>
+        <v>464953</v>
       </c>
       <c r="R73" t="n">
-        <v>6822536</v>
+        <v>6822673</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8050,12 +7654,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8082,15 +7686,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117711750</v>
+        <v>117711718</v>
       </c>
       <c r="B74" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8098,21 +7697,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8122,10 +7721,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>465035</v>
+        <v>464807</v>
       </c>
       <c r="R74" t="n">
-        <v>6822499</v>
+        <v>6822845</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8152,12 +7751,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8184,15 +7783,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117711466</v>
+        <v>117711719</v>
       </c>
       <c r="B75" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8200,21 +7794,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8224,10 +7818,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>464808</v>
+        <v>464779</v>
       </c>
       <c r="R75" t="n">
-        <v>6822742</v>
+        <v>6822837</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8254,12 +7848,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8286,15 +7880,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117711516</v>
+        <v>117711720</v>
       </c>
       <c r="B76" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8302,21 +7891,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8326,10 +7915,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>464802</v>
+        <v>464788</v>
       </c>
       <c r="R76" t="n">
-        <v>6822558</v>
+        <v>6822732</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8388,15 +7977,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117711694</v>
+        <v>117711721</v>
       </c>
       <c r="B77" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8428,10 +8012,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>465016</v>
+        <v>464811</v>
       </c>
       <c r="R77" t="n">
-        <v>6822483</v>
+        <v>6822558</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8458,12 +8042,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8490,15 +8074,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117711840</v>
+        <v>117711722</v>
       </c>
       <c r="B78" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8506,21 +8085,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8530,10 +8109,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>464918</v>
+        <v>464796</v>
       </c>
       <c r="R78" t="n">
-        <v>6822794</v>
+        <v>6822550</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8560,12 +8139,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8592,15 +8171,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117711667</v>
+        <v>117711723</v>
       </c>
       <c r="B79" t="n">
-        <v>78221</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8608,21 +8182,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8632,10 +8206,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>464785</v>
+        <v>464798</v>
       </c>
       <c r="R79" t="n">
-        <v>6822821</v>
+        <v>6822515</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8694,37 +8268,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117711982</v>
+        <v>117711724</v>
       </c>
       <c r="B80" t="n">
-        <v>94507</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2170</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8737,7 +8306,7 @@
         <v>464829</v>
       </c>
       <c r="R80" t="n">
-        <v>6822608</v>
+        <v>6822493</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8796,15 +8365,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117711499</v>
+        <v>117711466</v>
       </c>
       <c r="B81" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8836,10 +8400,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>464873</v>
+        <v>464808</v>
       </c>
       <c r="R81" t="n">
-        <v>6822661</v>
+        <v>6822742</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8866,12 +8430,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8898,15 +8462,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117711517</v>
+        <v>117711492</v>
       </c>
       <c r="B82" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8938,10 +8497,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>464796</v>
+        <v>465025</v>
       </c>
       <c r="R82" t="n">
-        <v>6822550</v>
+        <v>6822860</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8968,12 +8527,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9000,15 +8559,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>117711513</v>
+        <v>117711495</v>
       </c>
       <c r="B83" t="n">
-        <v>79102</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9040,10 +8594,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>464787</v>
+        <v>464963</v>
       </c>
       <c r="R83" t="n">
-        <v>6822645</v>
+        <v>6822863</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9070,12 +8624,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-06-09</t>
+          <t>2024-06-10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9102,15 +8656,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117711719</v>
+        <v>117711496</v>
       </c>
       <c r="B84" t="n">
-        <v>78220</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9118,21 +8667,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9142,10 +8691,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>464779</v>
+        <v>464827</v>
       </c>
       <c r="R84" t="n">
-        <v>6822837</v>
+        <v>6822493</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9204,37 +8753,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117711614</v>
+        <v>117711497</v>
       </c>
       <c r="B85" t="n">
-        <v>78510</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9244,10 +8788,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>464794</v>
+        <v>464842</v>
       </c>
       <c r="R85" t="n">
-        <v>6822546</v>
+        <v>6822509</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9306,37 +8850,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117711622</v>
+        <v>117711498</v>
       </c>
       <c r="B86" t="n">
-        <v>79593</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9346,10 +8885,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>464806</v>
+        <v>464862</v>
       </c>
       <c r="R86" t="n">
-        <v>6822865</v>
+        <v>6822596</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9408,15 +8947,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117711749</v>
+        <v>117711499</v>
       </c>
       <c r="B87" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9424,21 +8958,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9448,10 +8982,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>465020</v>
+        <v>464873</v>
       </c>
       <c r="R87" t="n">
-        <v>6822478</v>
+        <v>6822661</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9478,12 +9012,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9510,15 +9044,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117711757</v>
+        <v>117711500</v>
       </c>
       <c r="B88" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9526,21 +9055,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9550,10 +9079,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>464957</v>
+        <v>464862</v>
       </c>
       <c r="R88" t="n">
-        <v>6822685</v>
+        <v>6822691</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9580,12 +9109,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9612,15 +9141,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117711755</v>
+        <v>117711502</v>
       </c>
       <c r="B89" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9628,21 +9152,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9652,10 +9176,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>464952</v>
+        <v>464832</v>
       </c>
       <c r="R89" t="n">
-        <v>6822727</v>
+        <v>6822695</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9682,12 +9206,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-06-10</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9714,53 +9238,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117711573</v>
+        <v>117711504</v>
       </c>
       <c r="B90" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>464830</v>
+        <v>464812</v>
       </c>
       <c r="R90" t="n">
-        <v>6822871</v>
+        <v>6822865</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9795,18 +9311,12 @@
           <t>2024-06-09</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9825,59 +9335,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119549063</v>
+        <v>117711505</v>
       </c>
       <c r="B91" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>464809</v>
+        <v>464698</v>
       </c>
       <c r="R91" t="n">
-        <v>6822528</v>
+        <v>6822888</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9904,12 +9400,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9936,15 +9432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119549083</v>
+        <v>117711506</v>
       </c>
       <c r="B92" t="n">
-        <v>77910</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9952,21 +9443,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9976,10 +9467,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>465017</v>
+        <v>464705</v>
       </c>
       <c r="R92" t="n">
-        <v>6822483</v>
+        <v>6822862</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10006,12 +9497,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10038,59 +9529,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119549078</v>
+        <v>117711508</v>
       </c>
       <c r="B93" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Stygguggen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>464804</v>
+        <v>464807</v>
       </c>
       <c r="R93" t="n">
-        <v>6822584</v>
+        <v>6822845</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10117,12 +9594,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10149,15 +9626,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119549058</v>
+        <v>117711509</v>
       </c>
       <c r="B94" t="n">
-        <v>79144</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10189,10 +9661,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>464949</v>
+        <v>464812</v>
       </c>
       <c r="R94" t="n">
-        <v>6822470</v>
+        <v>6822825</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10219,12 +9691,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-09-04</t>
+          <t>2024-06-09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10248,6 +9720,4086 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>117711510</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>464779</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6822835</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>117711511</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>464789</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6822733</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>117711512</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>464797</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6822693</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>117711513</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>464787</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6822645</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>117711514</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>464789</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6822646</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>117711515</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>464791</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6822636</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>117711516</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>464802</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6822558</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>117711517</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>464796</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6822550</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>117711518</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>464788</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6822536</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>117711519</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>464829</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6822493</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>117711521</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>464823</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6822473</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>119549058</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>464949</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6822470</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>117711589</v>
+      </c>
+      <c r="B107" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>464773</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6822810</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>117711673</v>
+      </c>
+      <c r="B108" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>465070</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6822491</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>117711617</v>
+      </c>
+      <c r="B109" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>464933</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6822795</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>117711621</v>
+      </c>
+      <c r="B110" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>464960</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6822857</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>117711622</v>
+      </c>
+      <c r="B111" t="n">
+        <v>80460</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>464806</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6822865</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>117711555</v>
+      </c>
+      <c r="B112" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>464989</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6822826</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>117711556</v>
+      </c>
+      <c r="B113" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>464979</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6822661</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>117711558</v>
+      </c>
+      <c r="B114" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>465071</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6822559</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>117711559</v>
+      </c>
+      <c r="B115" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>465044</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6822619</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>117711561</v>
+      </c>
+      <c r="B116" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>464971</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6822628</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>117711568</v>
+      </c>
+      <c r="B117" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>464916</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6822882</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117711570</v>
+      </c>
+      <c r="B118" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>464946</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6822832</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>117711572</v>
+      </c>
+      <c r="B119" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>464937</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6822773</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>117711573</v>
+      </c>
+      <c r="B120" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>464830</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6822871</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>119549061</v>
+      </c>
+      <c r="B121" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>464836</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6822901</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>117711578</v>
+      </c>
+      <c r="B122" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>464962</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6822707</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>119549068</v>
+      </c>
+      <c r="B123" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>464828</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6822473</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>117711378</v>
+      </c>
+      <c r="B124" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>465023</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6822630</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>117711650</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>464992</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6822675</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2024-06-10</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>117711663</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>464857</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6822584</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>117711664</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>464835</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6822696</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>117711665</v>
+      </c>
+      <c r="B128" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>464884</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6822807</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>117711666</v>
+      </c>
+      <c r="B129" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>464698</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6822888</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>117711667</v>
+      </c>
+      <c r="B130" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>464785</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6822821</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>117711668</v>
+      </c>
+      <c r="B131" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>464814</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6822561</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>117711670</v>
+      </c>
+      <c r="B132" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>464796</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6822550</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>117711671</v>
+      </c>
+      <c r="B133" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>464829</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6822493</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>119549066</v>
+      </c>
+      <c r="B134" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>464942</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6822454</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>117711526</v>
+      </c>
+      <c r="B135" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Stygguggen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>464802</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6822558</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2024-06-09</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47905-2023 artfynd.xlsx
+++ b/artfynd/A 47905-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY135"/>
+  <dimension ref="A1:AZ135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711411</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711412</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711413</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711415</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711996</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711997</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711998</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711999</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117712000</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711982</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1845,6 +1905,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549078</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1951,6 +2016,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549062</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2057,6 +2127,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549063</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2154,6 +2229,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711748</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2251,6 +2331,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711749</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2348,6 +2433,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711750</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2445,6 +2535,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711751</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2542,6 +2637,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711752</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2639,6 +2739,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711753</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2736,6 +2841,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711755</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2833,6 +2943,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711756</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2930,6 +3045,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711757</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3027,6 +3147,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711759</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3124,6 +3249,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711761</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3221,6 +3351,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711762</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3318,6 +3453,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711763</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3415,6 +3555,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711839</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3512,6 +3657,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711840</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3609,6 +3759,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711907</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3706,6 +3861,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711929</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3803,6 +3963,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711930</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3900,6 +4065,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711931</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3997,6 +4167,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711932</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4094,6 +4269,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711933</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4191,6 +4371,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711934</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4288,6 +4473,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711935</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4385,6 +4575,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711936</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4482,6 +4677,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711937</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4579,6 +4779,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711938</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4676,6 +4881,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711939</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4773,6 +4983,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711940</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4870,6 +5085,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711941</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4967,6 +5187,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711942</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5064,6 +5289,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711943</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5161,6 +5391,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711944</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5258,6 +5493,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711947</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5355,6 +5595,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711948</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5452,6 +5697,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711950</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5549,6 +5799,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711952</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5646,6 +5901,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711953</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5743,6 +6003,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711954</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5840,6 +6105,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711955</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5937,6 +6207,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711956</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6034,6 +6309,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711957</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6131,6 +6411,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711959</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6228,6 +6513,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711960</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6325,6 +6615,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711961</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6422,6 +6717,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711962</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6519,6 +6819,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711963</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6616,6 +6921,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711964</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6713,6 +7023,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711965</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6810,6 +7125,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711966</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6907,6 +7227,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711967</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7004,6 +7329,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711968</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7101,6 +7431,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711969</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7198,6 +7533,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711972</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7295,6 +7635,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711613</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7392,6 +7737,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711614</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7489,6 +7839,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549083</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7586,6 +7941,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711694</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7683,6 +8043,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711695</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7780,6 +8145,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711718</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7877,6 +8247,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711719</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7974,6 +8349,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711720</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8071,6 +8451,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711721</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8168,6 +8553,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711722</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8265,6 +8655,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711723</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8362,6 +8757,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711724</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8459,6 +8859,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711466</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8556,6 +8961,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711492</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8653,6 +9063,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711495</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8750,6 +9165,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711496</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8847,6 +9267,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711497</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8944,6 +9369,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711498</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9041,6 +9471,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711499</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9138,6 +9573,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711500</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9235,6 +9675,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711502</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9332,6 +9777,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711504</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9429,6 +9879,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711505</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9526,6 +9981,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711506</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9623,6 +10083,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711508</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9720,6 +10185,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711509</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9817,6 +10287,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711510</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9914,6 +10389,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711511</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10011,6 +10491,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711512</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10108,6 +10593,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711513</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10205,6 +10695,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711514</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10302,6 +10797,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711515</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10399,6 +10899,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711516</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10496,6 +11001,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711517</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10593,6 +11103,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711518</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10690,6 +11205,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711519</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10787,6 +11307,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711521</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10884,6 +11409,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549058</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10981,6 +11511,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711589</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11078,6 +11613,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711673</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11175,6 +11715,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711617</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11272,6 +11817,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711621</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11369,6 +11919,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711622</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11475,6 +12030,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711555</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11581,6 +12141,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711556</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11687,6 +12252,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711558</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11793,6 +12363,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711559</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11899,6 +12474,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711561</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12005,6 +12585,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711568</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12111,6 +12696,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711570</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12217,6 +12807,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711572</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12323,6 +12918,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711573</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12420,6 +13020,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549061</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12525,6 +13130,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711578</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12626,6 +13236,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549068</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12733,6 +13348,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711378</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12830,6 +13450,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711650</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12927,6 +13552,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711663</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13024,6 +13654,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711664</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13121,6 +13756,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711665</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13218,6 +13858,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711666</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13315,6 +13960,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711667</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13412,6 +14062,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711668</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13509,6 +14164,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711670</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13606,6 +14266,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711671</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13703,6 +14368,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119549066</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13800,8 +14470,149 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117711526</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>